--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -2626,7 +2626,7 @@
         <x:v>告警灯高有效：电压 sensor 越限时点亮，电压告警解除后熄灭；BMC watchdog timeout 或 BIOS 启动 300 秒超时失败时锁存点亮，需重启解除。</x:v>
       </x:c>
       <x:c r="H5" s="2" t="str">
-        <x:v>GPIOI5 作为 gpio-led；ceb-gnrd-alert-led 服务监听 sensor/Watchdog/BIOS boot 状态并控制输出。</x:v>
+        <x:v>GPIOI5 作为 gpio-led；ceb-gnrd-alert-led 服务监听 sensor/Watchdog/BIOS boot 状态并控制输出；电压告警读取 Warning/Critical/PerformanceLoss/SoftShutdown/HardShutdown 阈值接口（ADC 的 UNR/LNR 对应 HardShutdown）。</x:v>
       </x:c>
       <x:c r="I5" s="2" t="str">
         <x:v>策略及 GPIO 服务已配置；目标机验证告警置位、解除和锁存行为。</x:v>
@@ -2684,7 +2684,7 @@
         <x:v>CPLD BMC health heartbeat input</x:v>
       </x:c>
       <x:c r="F7" s="3" t="str">
-        <x:v>BMC 心跳输出，等待 eSPI 主机流量后启用</x:v>
+        <x:v>BMC 心跳输出，eSPI Peripheral 驱动 SW_READY 后启用</x:v>
       </x:c>
       <x:c r="G7" s="3" t="str">
         <x:v>BMC 启动后，在 AST2600 eSPI Peripheral 驱动绑定并完成 SW_READY 初始化时启动周期心跳；不等待 BIOS/Host 实际流量。</x:v>
@@ -2696,7 +2696,7 @@
         <x:v>启动门控已配置；验证 SW_READY 条件、心跳波形及 CPLD 输入极性。</x:v>
       </x:c>
       <x:c r="J7" s="3" t="str">
-        <x:v>recipes-kernel/linux/files/aspeed-ceb-gnrd.dts; recipes-phosphor/leds/ceb-gnrd-espi-heartbeat.bb; recipes-phosphor/leds/files/wait-for-host-post.sh; recipes-phosphor/configuration/files/ceb-gnrd-hardware-contract.yaml; 用户提供的原理图/接口表</x:v>
+        <x:v>recipes-kernel/linux/files/aspeed-ceb-gnrd.dts; recipes-phosphor/leds/ceb-gnrd-espi-heartbeat.bb; recipes-phosphor/leds/files/wait-for-espi-driver.sh; recipes-phosphor/leds/files/ceb-gnrd-espi-heartbeat.service; recipes-phosphor/configuration/files/ceb-gnrd-hardware-contract.yaml; 用户提供的原理图/接口表</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="60" customHeight="1">
@@ -3169,8 +3169,8 @@
       <x:c r="G22" s="3" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="H22" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H22" s="3" t="str">
+        <x:v>adc0 ch0 (pad ADC0) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
         <x:v>111</x:v>
@@ -3201,8 +3201,8 @@
       <x:c r="G23" s="3" t="s">
         <x:v>117</x:v>
       </x:c>
-      <x:c r="H23" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H23" s="3" t="str">
+        <x:v>adc0 ch1 (pad ADC1) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
         <x:v>111</x:v>
@@ -3233,8 +3233,8 @@
       <x:c r="G24" s="3" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="H24" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H24" s="3" t="str">
+        <x:v>adc0 ch2 (pad ADC2) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
         <x:v>111</x:v>
@@ -3265,8 +3265,8 @@
       <x:c r="G25" s="3" t="s">
         <x:v>127</x:v>
       </x:c>
-      <x:c r="H25" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H25" s="3" t="str">
+        <x:v>adc0 ch3 (pad ADC3) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
         <x:v>111</x:v>
@@ -3297,8 +3297,8 @@
       <x:c r="G26" s="3" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="H26" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H26" s="3" t="str">
+        <x:v>adc0 ch4 (pad ADC4) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
         <x:v>111</x:v>
@@ -3329,8 +3329,8 @@
       <x:c r="G27" s="3" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="H27" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H27" s="3" t="str">
+        <x:v>adc0 ch5 (pad ADC5) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
         <x:v>111</x:v>
@@ -3361,8 +3361,8 @@
       <x:c r="G28" s="3" t="s">
         <x:v>142</x:v>
       </x:c>
-      <x:c r="H28" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H28" s="3" t="str">
+        <x:v>adc0 ch6 (pad ADC6) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
         <x:v>111</x:v>
@@ -3393,8 +3393,8 @@
       <x:c r="G29" s="3" t="s">
         <x:v>147</x:v>
       </x:c>
-      <x:c r="H29" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H29" s="3" t="str">
+        <x:v>adc0 ch7 (pad ADC7) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
         <x:v>111</x:v>
@@ -3407,8 +3407,8 @@
       <x:c r="A30" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B30" s="3" t="s">
-        <x:v>148</x:v>
+      <x:c r="B30" s="3" t="str">
+        <x:v>ADC1 channel 0</x:v>
       </x:c>
       <x:c r="C30" s="3" t="s">
         <x:v>149</x:v>
@@ -3425,8 +3425,8 @@
       <x:c r="G30" s="3" t="s">
         <x:v>152</x:v>
       </x:c>
-      <x:c r="H30" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H30" s="3" t="str">
+        <x:v>adc1 ch0 (pad ADC8) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
         <x:v>111</x:v>
@@ -3439,8 +3439,8 @@
       <x:c r="A31" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B31" s="3" t="s">
-        <x:v>153</x:v>
+      <x:c r="B31" s="3" t="str">
+        <x:v>ADC1 channel 1</x:v>
       </x:c>
       <x:c r="C31" s="3" t="s">
         <x:v>154</x:v>
@@ -3457,8 +3457,8 @@
       <x:c r="G31" s="3" t="s">
         <x:v>157</x:v>
       </x:c>
-      <x:c r="H31" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H31" s="3" t="str">
+        <x:v>adc1 ch1 (pad ADC9) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
         <x:v>111</x:v>
@@ -3471,8 +3471,8 @@
       <x:c r="A32" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B32" s="3" t="s">
-        <x:v>158</x:v>
+      <x:c r="B32" s="3" t="str">
+        <x:v>ADC1 channel 2</x:v>
       </x:c>
       <x:c r="C32" s="3" t="s">
         <x:v>159</x:v>
@@ -3489,8 +3489,8 @@
       <x:c r="G32" s="3" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="H32" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H32" s="3" t="str">
+        <x:v>adc1 ch2 (pad ADC10) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
         <x:v>111</x:v>
@@ -3503,8 +3503,8 @@
       <x:c r="A33" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B33" s="3" t="s">
-        <x:v>163</x:v>
+      <x:c r="B33" s="3" t="str">
+        <x:v>ADC1 channel 3</x:v>
       </x:c>
       <x:c r="C33" s="3" t="s">
         <x:v>164</x:v>
@@ -3521,8 +3521,8 @@
       <x:c r="G33" s="3" t="s">
         <x:v>167</x:v>
       </x:c>
-      <x:c r="H33" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H33" s="3" t="str">
+        <x:v>adc1 ch3 (pad ADC11) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
         <x:v>111</x:v>
@@ -3535,8 +3535,8 @@
       <x:c r="A34" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B34" s="3" t="s">
-        <x:v>168</x:v>
+      <x:c r="B34" s="3" t="str">
+        <x:v>ADC1 channel 4</x:v>
       </x:c>
       <x:c r="C34" s="3" t="s">
         <x:v>169</x:v>
@@ -3553,8 +3553,8 @@
       <x:c r="G34" s="3" t="s">
         <x:v>172</x:v>
       </x:c>
-      <x:c r="H34" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H34" s="3" t="str">
+        <x:v>adc1 ch4 (pad ADC12) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
         <x:v>111</x:v>
@@ -3567,8 +3567,8 @@
       <x:c r="A35" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B35" s="3" t="s">
-        <x:v>173</x:v>
+      <x:c r="B35" s="3" t="str">
+        <x:v>ADC1 channel 5</x:v>
       </x:c>
       <x:c r="C35" s="3" t="s">
         <x:v>174</x:v>
@@ -3585,8 +3585,8 @@
       <x:c r="G35" s="3" t="s">
         <x:v>177</x:v>
       </x:c>
-      <x:c r="H35" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H35" s="3" t="str">
+        <x:v>adc1 ch5 (pad ADC13) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
         <x:v>111</x:v>
@@ -3599,8 +3599,8 @@
       <x:c r="A36" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B36" s="3" t="s">
-        <x:v>178</x:v>
+      <x:c r="B36" s="3" t="str">
+        <x:v>ADC1 channel 6</x:v>
       </x:c>
       <x:c r="C36" s="3" t="s">
         <x:v>179</x:v>
@@ -3617,8 +3617,8 @@
       <x:c r="G36" s="3" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="H36" s="3" t="s">
-        <x:v>110</x:v>
+      <x:c r="H36" s="3" t="str">
+        <x:v>adc1 ch6 (pad ADC14) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
         <x:v>111</x:v>
@@ -3631,8 +3631,8 @@
       <x:c r="A37" s="3" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="B37" s="3" t="s">
-        <x:v>183</x:v>
+      <x:c r="B37" s="3" t="str">
+        <x:v>ADC1 channel 7</x:v>
       </x:c>
       <x:c r="C37" s="3" t="s">
         <x:v>184</x:v>
@@ -3646,14 +3646,14 @@
       <x:c r="F37" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G37" s="3" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="H37" s="3" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="I37" s="3" t="s">
-        <x:v>188</x:v>
+      <x:c r="G37" s="3" t="str">
+        <x:v>D3V0_BAT0 3 V 标称；ScaleFactor 1（板上无分压）；UNR/LNR ±15%</x:v>
+      </x:c>
+      <x:c r="H37" s="3" t="str">
+        <x:v>adc1 ch7 (pad ADC15) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+      </x:c>
+      <x:c r="I37" s="3" t="str">
+        <x:v>已按现板配置；R542/Q39 未焊，ADC 引脚上约 3 V 超出 2.5 V 量程，读数会饱和。需焊接 R542（÷2）后将 ScaleFactor 改为 2</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
         <x:v>112</x:v>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -2225,7 +2225,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="7">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -2261,6 +2261,17 @@
       <x:sz val="9"/>
       <x:name val="宋体"/>
     </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FFFF0000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFF0000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -2295,7 +2306,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="7">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2309,6 +2320,12 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="2">
     <x:cellStyle name="Normal" xfId="1"/>
@@ -3652,7 +3669,7 @@
       <x:c r="H37" s="3" t="str">
         <x:v>adc1 ch7 (pad ADC15) + iio-hwmon；Entity-Manager ADC sensor</x:v>
       </x:c>
-      <x:c r="I37" s="3" t="str">
+      <x:c r="I37" s="7" t="str">
         <x:v>已按现板配置；R542/Q39 未焊，ADC 引脚上约 3 V 超出 2.5 V 量程，读数会饱和。需焊接 R542（÷2）后将 ScaleFactor 改为 2</x:v>
       </x:c>
       <x:c r="J37" s="3" t="s">
@@ -6825,6 +6842,630 @@
       </x:c>
       <x:c r="J136" s="3" t="s">
         <x:v>736</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="24" customHeight="1">
+      <x:c r="A138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对象</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">涉及位置</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">球位 / 地址</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需确认方</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">疑问</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">当前代码现状</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">影响 / 建议</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J138" s="8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依据</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="110" customHeight="1">
+      <x:c r="A139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADC 参考电压</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADC0 / ADC1 全部通道</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AF19 / AF17 (ADCVREFEXT0/1)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EE / 硬件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原理图中 ADCVREFEXT0/1 接 P1V8_STBY；EE 分压表隐含使用内部 2.5 V 参考。实际选哪种参考电压未书面确认。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">设备树未设置 aspeed,int-vref-microvolt 或 vref-supply，依赖内核 g6 默认值（推测为内部 2.5 V）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">若实际为外部 1.8 V，PVCCIN_CPU、PVCCFA_EHV_CPU、PVCCINF_EHV_FIVRA_CPU、P1V8_STBY 将满量程饱和。建议确认后在 &amp;adc0/&amp;adc1 显式写出。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J139" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原理图 ADC 页；EE ADC 电压监控表；aspeed-ceb-gnrd.dts</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="110" customHeight="1">
+      <x:c r="A140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">D3V0_BAT0 分压</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADC1 channel 7 / ADC15</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AC17</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EE / 硬件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">R542 与 Q39 均未焊（NC），ADC 引脚上约 3 V，超出 2.5 V 量程；BMC_BAT_SENSE_EN 没有对应 GPIO 映射。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ScaleFactor 1（按现板），阈值 2.55 / 3.45 V 实际不可达。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">建议焊 R542（÷2）后改 ScaleFactor 2；若改用 Q39 采样开关，需新增 BMC_BAT_SENSE_EN GPIO 及控制逻辑。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J140" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原理图电池检测页；ceb-gnrd.json；ceb-gnrd-hardware-contract.yaml</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="110" customHeight="1">
+      <x:c r="A141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PSU 数量</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CRPS PMBus</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">I2C8 / 0x58 0x59 0x5A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EE / 产品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">机器配置声明 2 个热插拔 PSU（OBMC_POWER_SUPPLY_INSTANCES 为 0 1），但设备树和 Entity-Manager 配了 0x58/0x59/0x5A 三个地址。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pmbus@58/59/5a 与 CRPS0/1/2 均已配置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">确认实际 PSU 数量与地址；多余地址在空槽时会产生 probe 失败日志。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J141" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd.conf；aspeed-ceb-gnrd.dts；ceb-gnrd.json</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="110" customHeight="1">
+      <x:c r="A142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PCIe 槽位编号</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">I2C1-I2C6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC_SLOT1/3/4/5/6/7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EE / 硬件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">槽位编号为 1、3、4、5、6、7，没有 SLOT2 的 I2C 线路，是否为设计如此未确认。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">仅映射 6 路 PCIe 槽 I2C，IPMI Master Write-Read 白名单覆盖 i2c-0..5。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">确认 SLOT2 是否无 BMC 侧带管理总线；若存在需补充。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J142" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-hardware-contract.yaml；generate_i2c_allowlist.py</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="110" customHeight="1">
+      <x:c r="A143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">管理网口 PHY 模式</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MAC2 / RGMII2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RTL8211FS-CG</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EE / 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phy-mode 写为 rgmii，RTL8211F 通常需要 rgmii-id 或 rgmii-rxid，并结合 SCU 延时配置。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Linux 与 U-Boot 均为 phy-mode = rgmii，未设置 SCU 延时。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">实板验证 eth0 收发；链路异常时先改 phy-mode 或调整延时。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J143" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="110" customHeight="1">
+      <x:c r="A144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RTC 驱动兼容性</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">I2C10 / 0x6F</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NCT3015Y-R</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">器件为 NCT3015Y-R，设备树使用 nuvoton,nct3018y（该驱动唯一的 compatible），两者寄存器兼容性未在目标机验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CONFIG_RTC_DRV_NCT3018Y=y；rtc@6f 使用 nuvoton,nct3018y。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上板确认 /sys/class/rtc/rtc0/name 并用 hwclock 读写验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；espi-peci.cfg</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="110" customHeight="1">
+      <x:c r="A145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上电恢复策略</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Host 电源恢复</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">产品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">注释写“恢复上一次主机电源状态”，代码却把默认策略改成 AlwaysOn，两者矛盾。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-settings-defaults-native.bbappend 将 AlwaysOff 替换为 AlwaysOn。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">确认期望策略（AlwaysOn / Restore），统一注释与代码。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-settings-defaults-native.bbappend</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="110" customHeight="1">
+      <x:c r="A146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CFG_VER1 strap</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GPIO strap</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待定</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">EE / 硬件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">硬件合同中有 CFG_VER1，GPIO 映射待定，本表和设备树均未命名。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">合同标记 exact_gpio_mapping_pending；设备树只命名 CFG_VER0。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">确认 CFG_VER1 的 GPIO 与用途后补充 gpio-line-names 和本表。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-hardware-contract.yaml</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="110" customHeight="1">
+      <x:c r="A147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FRU 实体 ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">motherboard FRU</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">FRUID 0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件 / 产品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-ipmi-fru.yaml 中保留 TODO，entityID 7 / entityInstance 1 是否符合平台 IPMI 实体定义未确认。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">使用默认值 entityID 7、entityInstance 1。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">确认后删除 TODO。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-ipmi-fru.yaml</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="110" customHeight="1">
+      <x:c r="A148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">告警 LED 服务</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC_SYS_ALERT_LED</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GPIOI5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">服务通过 busctl 解析 JSON 并监听 Watchdog Timeout 信号，接口名 xyz.openbmc_project.Watchdog 与 JSON 解析格式未在目标机验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已兼容 busctl 返回值外层列表和变体格式，并读取 Warning 至 HardShutdown 全部阈值接口。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">目标机验证电压越限点亮、解除熄灭、watchdog 锁存三种行为。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-alert-led.py</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="110" customHeight="1">
+      <x:c r="A149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">构建适配</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">内核 / U-Boot / IPMI / 电源控制</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">以下内容尚未构建验证：内核 eSPI、chassis 补丁能否应用于 linux-aspeed；U-Boot 2019.04 是否识别 bootph-all；IPMI mc info 补丁已改为 libgpiod 1.x 接口；x86-power-control 的 button-passthrough 与 chassis-system-reset meson 选项是否存在。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">相关文件已就位，但没有 bitbake 构建结果。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">在 Linux 构建主机执行 bitbake obmc-phosphor-image，按报错修正。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">linux-aspeed_%.bbappend；u-boot-aspeed-sdk_%.bbappend；phosphor-ipmi-host_%.bbappend；x86-power-control_%.bbappend</x:t>
+        </x:is>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -2933,8 +2933,8 @@
       <x:c r="H14" s="3" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="I14" s="3" t="s">
-        <x:v>66</x:v>
+      <x:c r="I14" s="3" t="str">
+        <x:v>不应误计入 PCB revision；CFG_VER1 为硬件预留，无需配置</x:v>
       </x:c>
       <x:c r="J14" s="3" t="s">
         <x:v>18</x:v>
@@ -3187,7 +3187,7 @@
         <x:v>109</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
-        <x:v>adc0 ch0 (pad ADC0) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch0 (pad ADC0) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I22" s="3" t="s">
         <x:v>111</x:v>
@@ -3219,7 +3219,7 @@
         <x:v>117</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
-        <x:v>adc0 ch1 (pad ADC1) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch1 (pad ADC1) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I23" s="3" t="s">
         <x:v>111</x:v>
@@ -3251,7 +3251,7 @@
         <x:v>122</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
-        <x:v>adc0 ch2 (pad ADC2) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch2 (pad ADC2) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I24" s="3" t="s">
         <x:v>111</x:v>
@@ -3283,7 +3283,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="H25" s="3" t="str">
-        <x:v>adc0 ch3 (pad ADC3) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch3 (pad ADC3) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I25" s="3" t="s">
         <x:v>111</x:v>
@@ -3315,7 +3315,7 @@
         <x:v>132</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
-        <x:v>adc0 ch4 (pad ADC4) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch4 (pad ADC4) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I26" s="3" t="s">
         <x:v>111</x:v>
@@ -3347,7 +3347,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
-        <x:v>adc0 ch5 (pad ADC5) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch5 (pad ADC5) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I27" s="3" t="s">
         <x:v>111</x:v>
@@ -3379,7 +3379,7 @@
         <x:v>142</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
-        <x:v>adc0 ch6 (pad ADC6) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch6 (pad ADC6) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I28" s="3" t="s">
         <x:v>111</x:v>
@@ -3411,7 +3411,7 @@
         <x:v>147</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
-        <x:v>adc0 ch7 (pad ADC7) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc0 ch7 (pad ADC7) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I29" s="3" t="s">
         <x:v>111</x:v>
@@ -3443,7 +3443,7 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
-        <x:v>adc1 ch0 (pad ADC8) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch0 (pad ADC8) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I30" s="3" t="s">
         <x:v>111</x:v>
@@ -3475,7 +3475,7 @@
         <x:v>157</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
-        <x:v>adc1 ch1 (pad ADC9) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch1 (pad ADC9) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I31" s="3" t="s">
         <x:v>111</x:v>
@@ -3507,7 +3507,7 @@
         <x:v>162</x:v>
       </x:c>
       <x:c r="H32" s="3" t="str">
-        <x:v>adc1 ch2 (pad ADC10) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch2 (pad ADC10) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I32" s="3" t="s">
         <x:v>111</x:v>
@@ -3539,7 +3539,7 @@
         <x:v>167</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
-        <x:v>adc1 ch3 (pad ADC11) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch3 (pad ADC11) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I33" s="3" t="s">
         <x:v>111</x:v>
@@ -3571,7 +3571,7 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
-        <x:v>adc1 ch4 (pad ADC12) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch4 (pad ADC12) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I34" s="3" t="s">
         <x:v>111</x:v>
@@ -3603,7 +3603,7 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="H35" s="3" t="str">
-        <x:v>adc1 ch5 (pad ADC13) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch5 (pad ADC13) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I35" s="3" t="s">
         <x:v>111</x:v>
@@ -3635,7 +3635,7 @@
         <x:v>182</x:v>
       </x:c>
       <x:c r="H36" s="3" t="str">
-        <x:v>adc1 ch6 (pad ADC14) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch6 (pad ADC14) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I36" s="3" t="s">
         <x:v>111</x:v>
@@ -3667,7 +3667,7 @@
         <x:v>D3V0_BAT0 3 V 标称；ScaleFactor 1（板上无分压）；UNR/LNR ±15%</x:v>
       </x:c>
       <x:c r="H37" s="3" t="str">
-        <x:v>adc1 ch7 (pad ADC15) + iio-hwmon；Entity-Manager ADC sensor</x:v>
+        <x:v>adc1 ch7 (pad ADC15) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
       </x:c>
       <x:c r="I37" s="7" t="str">
         <x:v>已按现板配置；R542/Q39 未焊，ADC 引脚上约 3 V 超出 2.5 V 量程，读数会饱和。需焊接 R542（÷2）后将 ScaleFactor 改为 2</x:v>
@@ -4527,8 +4527,8 @@
       <x:c r="F64" s="3" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="G64" s="3" t="s">
-        <x:v>343</x:v>
+      <x:c r="G64" s="3" t="str">
+        <x:v>0x58/0x59/0x5A; input/output V and W; Linux bus i2c-7；机框内实际在位 0-2 个 PSU，地址不固定</x:v>
       </x:c>
       <x:c r="H64" s="3" t="s">
         <x:v>344</x:v>
@@ -4559,8 +4559,8 @@
       <x:c r="F65" s="3" t="s">
         <x:v>342</x:v>
       </x:c>
-      <x:c r="G65" s="3" t="s">
-        <x:v>343</x:v>
+      <x:c r="G65" s="3" t="str">
+        <x:v>0x58/0x59/0x5A; input/output V and W; Linux bus i2c-7；机框内实际在位 0-2 个 PSU，地址不固定</x:v>
       </x:c>
       <x:c r="H65" s="3" t="s">
         <x:v>344</x:v>
@@ -5682,8 +5682,8 @@
       <x:c r="G100" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H100" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H100" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I100" s="3" t="s">
         <x:v>566</x:v>
@@ -5714,8 +5714,8 @@
       <x:c r="G101" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H101" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H101" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I101" s="3" t="s">
         <x:v>566</x:v>
@@ -5746,8 +5746,8 @@
       <x:c r="G102" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H102" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H102" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I102" s="3" t="s">
         <x:v>566</x:v>
@@ -5778,8 +5778,8 @@
       <x:c r="G103" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H103" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H103" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I103" s="3" t="s">
         <x:v>566</x:v>
@@ -5810,8 +5810,8 @@
       <x:c r="G104" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H104" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H104" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I104" s="3" t="s">
         <x:v>566</x:v>
@@ -5842,8 +5842,8 @@
       <x:c r="G105" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H105" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H105" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I105" s="3" t="s">
         <x:v>566</x:v>
@@ -5874,8 +5874,8 @@
       <x:c r="G106" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H106" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H106" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I106" s="3" t="s">
         <x:v>566</x:v>
@@ -5906,8 +5906,8 @@
       <x:c r="G107" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H107" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H107" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I107" s="3" t="s">
         <x:v>566</x:v>
@@ -5938,8 +5938,8 @@
       <x:c r="G108" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H108" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H108" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I108" s="3" t="s">
         <x:v>566</x:v>
@@ -5970,8 +5970,8 @@
       <x:c r="G109" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H109" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H109" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I109" s="3" t="s">
         <x:v>566</x:v>
@@ -6002,8 +6002,8 @@
       <x:c r="G110" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H110" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H110" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I110" s="3" t="s">
         <x:v>566</x:v>
@@ -6034,8 +6034,8 @@
       <x:c r="G111" s="3" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="H111" s="3" t="s">
-        <x:v>565</x:v>
+      <x:c r="H111" s="3" t="str">
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
       </x:c>
       <x:c r="I111" s="3" t="s">
         <x:v>566</x:v>
@@ -6896,7 +6896,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="139" ht="110" customHeight="1">
+    <x:row r="139" ht="125" customHeight="1">
       <x:c r="A139" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">待澄清</x:t>
@@ -6904,17 +6904,17 @@
       </x:c>
       <x:c r="B139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ADC 参考电压</x:t>
+          <x:t xml:space="preserve">D3V0_BAT0 分压</x:t>
         </x:is>
       </x:c>
       <x:c r="C139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ADC0 / ADC1 全部通道</x:t>
+          <x:t xml:space="preserve">ADC1 channel 7 / ADC15</x:t>
         </x:is>
       </x:c>
       <x:c r="D139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AF19 / AF17 (ADCVREFEXT0/1)</x:t>
+          <x:t xml:space="preserve">AC17</x:t>
         </x:is>
       </x:c>
       <x:c r="E139" s="7" t="inlineStr">
@@ -6929,26 +6929,26 @@
       </x:c>
       <x:c r="G139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">原理图中 ADCVREFEXT0/1 接 P1V8_STBY；EE 分压表隐含使用内部 2.5 V 参考。实际选哪种参考电压未书面确认。</x:t>
+          <x:t xml:space="preserve">R542 与 Q39 均未焊（NC），ADC 引脚上约 3 V，超出 2.5 V 量程；BMC_BAT_SENSE_EN 没有对应 GPIO 映射。</x:t>
         </x:is>
       </x:c>
       <x:c r="H139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">设备树未设置 aspeed,int-vref-microvolt 或 vref-supply，依赖内核 g6 默认值（推测为内部 2.5 V）。</x:t>
+          <x:t xml:space="preserve">ScaleFactor 1（按现板），阈值 2.55 / 3.45 V 实际不可达。</x:t>
         </x:is>
       </x:c>
       <x:c r="I139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">若实际为外部 1.8 V，PVCCIN_CPU、PVCCFA_EHV_CPU、PVCCINF_EHV_FIVRA_CPU、P1V8_STBY 将满量程饱和。建议确认后在 &amp;adc0/&amp;adc1 显式写出。</x:t>
+          <x:t xml:space="preserve">建议焊 R542（÷2）后改 ScaleFactor 2；若改用 Q39 采样开关，需新增 BMC_BAT_SENSE_EN GPIO 及控制逻辑。</x:t>
         </x:is>
       </x:c>
       <x:c r="J139" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">原理图 ADC 页；EE ADC 电压监控表；aspeed-ceb-gnrd.dts</x:t>
+          <x:t xml:space="preserve">原理图电池检测页；ceb-gnrd.json；ceb-gnrd-hardware-contract.yaml</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="140" ht="110" customHeight="1">
+    <x:row r="140" ht="125" customHeight="1">
       <x:c r="A140" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">待澄清</x:t>
@@ -6956,17 +6956,17 @@
       </x:c>
       <x:c r="B140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">D3V0_BAT0 分压</x:t>
+          <x:t xml:space="preserve">BIOS 与 BMC 的 eSPI SIO 访问</x:t>
         </x:is>
       </x:c>
       <x:c r="C140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ADC1 channel 7 / ADC15</x:t>
+          <x:t xml:space="preserve">eSPI Peripheral 通道 / 端口 0x2E 0x2F</x:t>
         </x:is>
       </x:c>
       <x:c r="D140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AC17</x:t>
+          <x:t xml:space="preserve">CPU_ESPI_IO0-3、CLK、CS0、ALERT、RSTN</x:t>
         </x:is>
       </x:c>
       <x:c r="E140" s="7" t="inlineStr">
@@ -6976,31 +6976,31 @@
       </x:c>
       <x:c r="F140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EE / 硬件</x:t>
+          <x:t xml:space="preserve">BIOS / 软件</x:t>
         </x:is>
       </x:c>
       <x:c r="G140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">R542 与 Q39 均未焊（NC），ADC 引脚上约 3 V，超出 2.5 V 量程；BMC_BAT_SENSE_EN 没有对应 GPIO 映射。</x:t>
+          <x:t xml:space="preserve">分析仪抓包显示 BIOS 反复访问 SIO 配置端口 0x2E/0x2F（写 0xA5 解锁、选择逻辑设备、读 0x20 得到 0x26），多次出现 WAIT_STATE 重试，并有 Reserved(0E) 无效响应（Slave Status Not Available）后 BIOS 重试。</x:t>
         </x:is>
       </x:c>
       <x:c r="H140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ScaleFactor 1（按现板），阈值 2.55 / 3.45 V 实际不可达。</x:t>
+          <x:t xml:space="preserve">BMC 仅在内核驱动中置位 Peripheral SW_READY 并在 eSPI 复位后重新置位，SIO 访问完全由 AST2600 硬件完成；驱动没有错误中断处理、日志或计数，也没有 SIO 使能配置。</x:t>
         </x:is>
       </x:c>
       <x:c r="I140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建议焊 R542（÷2）后改 ScaleFactor 2；若改用 Q39 采样开关，需新增 BMC_BAT_SENSE_EN GPIO 及控制逻辑。</x:t>
+          <x:t xml:space="preserve">无法从代码判断是否为硬件时序或 BMC 侧使能问题。建议在目标机读取 eSPI 控制/中断状态寄存器，确认 SIO 解码是否已使能，并让 BIOS 侧确认 0E 响应后是否重试成功。</x:t>
         </x:is>
       </x:c>
       <x:c r="J140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">原理图电池检测页；ceb-gnrd.json；ceb-gnrd-hardware-contract.yaml</x:t>
+          <x:t xml:space="preserve">aspeed-espi-peripheral 补丁；README eSPI 章节；分析仪抓包</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="141" ht="110" customHeight="1">
+    <x:row r="141" ht="125" customHeight="1">
       <x:c r="A141" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">待澄清</x:t>
@@ -7008,17 +7008,17 @@
       </x:c>
       <x:c r="B141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PSU 数量</x:t>
+          <x:t xml:space="preserve">管理网口 PHY 模式</x:t>
         </x:is>
       </x:c>
       <x:c r="C141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CRPS PMBus</x:t>
+          <x:t xml:space="preserve">MAC2 / RGMII2</x:t>
         </x:is>
       </x:c>
       <x:c r="D141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">I2C8 / 0x58 0x59 0x5A</x:t>
+          <x:t xml:space="preserve">RTL8211FS-CG</x:t>
         </x:is>
       </x:c>
       <x:c r="E141" s="7" t="inlineStr">
@@ -7028,31 +7028,31 @@
       </x:c>
       <x:c r="F141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EE / 产品</x:t>
+          <x:t xml:space="preserve">EE / 软件</x:t>
         </x:is>
       </x:c>
       <x:c r="G141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">机器配置声明 2 个热插拔 PSU（OBMC_POWER_SUPPLY_INSTANCES 为 0 1），但设备树和 Entity-Manager 配了 0x58/0x59/0x5A 三个地址。</x:t>
+          <x:t xml:space="preserve">已将 Linux 与 U-Boot 的 phy-mode 改为 rgmii-rxid（与 AST2600 EVB 的 MAC2 一致）。PHY 地址沿用 EVB 的 reg = 0，是否与 RTL8211FS 的地址 strap 一致未确认。</x:t>
         </x:is>
       </x:c>
       <x:c r="H141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">pmbus@58/59/5a 与 CRPS0/1/2 均已配置。</x:t>
+          <x:t xml:space="preserve">phy-mode = rgmii-rxid；ethphy1 reg = 0。</x:t>
         </x:is>
       </x:c>
       <x:c r="I141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">确认实际 PSU 数量与地址；多余地址在空槽时会产生 probe 失败日志。</x:t>
+          <x:t xml:space="preserve">实板验证 eth0 链路和收发；链路异常时先核对 PHY 地址和延时配置。</x:t>
         </x:is>
       </x:c>
       <x:c r="J141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ceb-gnrd.conf；aspeed-ceb-gnrd.dts；ceb-gnrd.json</x:t>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="142" ht="110" customHeight="1">
+    <x:row r="142" ht="125" customHeight="1">
       <x:c r="A142" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">待澄清</x:t>
@@ -7060,17 +7060,17 @@
       </x:c>
       <x:c r="B142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PCIe 槽位编号</x:t>
+          <x:t xml:space="preserve">RTC 驱动兼容性</x:t>
         </x:is>
       </x:c>
       <x:c r="C142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">I2C1-I2C6</x:t>
+          <x:t xml:space="preserve">I2C10 / 0x6F</x:t>
         </x:is>
       </x:c>
       <x:c r="D142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMC_SLOT1/3/4/5/6/7</x:t>
+          <x:t xml:space="preserve">NCT3015Y-R</x:t>
         </x:is>
       </x:c>
       <x:c r="E142" s="7" t="inlineStr">
@@ -7080,31 +7080,31 @@
       </x:c>
       <x:c r="F142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EE / 硬件</x:t>
+          <x:t xml:space="preserve">软件</x:t>
         </x:is>
       </x:c>
       <x:c r="G142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">槽位编号为 1、3、4、5、6、7，没有 SLOT2 的 I2C 线路，是否为设计如此未确认。</x:t>
+          <x:t xml:space="preserve">内核 rtc-nct3018y 的 compatible 和 binding 只写 NCT3018Y，没有提到 NCT3015Y。仓库内其他项目（如 nvidia）同样只启用 CONFIG_RTC_DRV_NCT3018Y，没有 NCT3015Y 的专门节点可参照。</x:t>
         </x:is>
       </x:c>
       <x:c r="H142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">仅映射 6 路 PCIe 槽 I2C，IPMI Master Write-Read 白名单覆盖 i2c-0..5。</x:t>
+          <x:t xml:space="preserve">沿用 nuvoton,nct3018y 与 CONFIG_RTC_DRV_NCT3018Y=y。</x:t>
         </x:is>
       </x:c>
       <x:c r="I142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">确认 SLOT2 是否无 BMC 侧带管理总线；若存在需补充。</x:t>
+          <x:t xml:space="preserve">上板确认 /sys/class/rtc/rtc0/name 并用 hwclock 读写验证。</x:t>
         </x:is>
       </x:c>
       <x:c r="J142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ceb-gnrd-hardware-contract.yaml；generate_i2c_allowlist.py</x:t>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；espi-peci.cfg</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="143" ht="110" customHeight="1">
+    <x:row r="143" ht="125" customHeight="1">
       <x:c r="A143" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">待澄清</x:t>
@@ -7112,17 +7112,17 @@
       </x:c>
       <x:c r="B143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">管理网口 PHY 模式</x:t>
+          <x:t xml:space="preserve">告警 LED 服务</x:t>
         </x:is>
       </x:c>
       <x:c r="C143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MAC2 / RGMII2</x:t>
+          <x:t xml:space="preserve">BMC_SYS_ALERT_LED</x:t>
         </x:is>
       </x:c>
       <x:c r="D143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RTL8211FS-CG</x:t>
+          <x:t xml:space="preserve">GPIOI5</x:t>
         </x:is>
       </x:c>
       <x:c r="E143" s="7" t="inlineStr">
@@ -7132,31 +7132,31 @@
       </x:c>
       <x:c r="F143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EE / 软件</x:t>
+          <x:t xml:space="preserve">软件</x:t>
         </x:is>
       </x:c>
       <x:c r="G143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">phy-mode 写为 rgmii，RTL8211F 通常需要 rgmii-id 或 rgmii-rxid，并结合 SCU 延时配置。</x:t>
+          <x:t xml:space="preserve">Watchdog 信号的接口名 xyz.openbmc_project.Watchdog 和成员 Timeout 已对照 phosphor-sel-logger 源码，与脚本一致；busctl 的 JSON 返回格式仍按文档处理，未在目标机验证。</x:t>
         </x:is>
       </x:c>
       <x:c r="H143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Linux 与 U-Boot 均为 phy-mode = rgmii，未设置 SCU 延时。</x:t>
+          <x:t xml:space="preserve">已兼容 busctl 返回值外层列表和变体格式，并读取 Warning 至 HardShutdown 全部阈值接口。</x:t>
         </x:is>
       </x:c>
       <x:c r="I143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">实板验证 eth0 收发；链路异常时先改 phy-mode 或调整延时。</x:t>
+          <x:t xml:space="preserve">目标机验证电压越限点亮、解除熄灭、watchdog 锁存三种行为。</x:t>
         </x:is>
       </x:c>
       <x:c r="J143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts</x:t>
+          <x:t xml:space="preserve">ceb-gnrd-alert-led.py；phosphor-sel-logger watchdog_event_monitor.hpp</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="144" ht="110" customHeight="1">
+    <x:row r="144" ht="125" customHeight="1">
       <x:c r="A144" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">待澄清</x:t>
@@ -7164,17 +7164,17 @@
       </x:c>
       <x:c r="B144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RTC 驱动兼容性</x:t>
+          <x:t xml:space="preserve">构建适配</x:t>
         </x:is>
       </x:c>
       <x:c r="C144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">I2C10 / 0x6F</x:t>
+          <x:t xml:space="preserve">内核 / U-Boot / IPMI / 电源控制</x:t>
         </x:is>
       </x:c>
       <x:c r="D144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NCT3015Y-R</x:t>
+          <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
       <x:c r="E144" s="7" t="inlineStr">
@@ -7189,282 +7189,22 @@
       </x:c>
       <x:c r="G144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">器件为 NCT3015Y-R，设备树使用 nuvoton,nct3018y（该驱动唯一的 compatible），两者寄存器兼容性未在目标机验证。</x:t>
+          <x:t xml:space="preserve">已核对：x86-power-control 存在 button-passthrough 与 chassis-system-reset 选项；内核 Kconfig、hwmon Makefile、g6 dtsi 的补丁上下文与 SRCREV 一致，eSPI 的 Makefile 行改由 bbappend 追加；U-Boot 设备树已删除不存在的 &amp;mdio2 和 fwspid/fwqspi pinctrl 引用，bootph-all 改为 u-boot,dm-pre-reloc。仍未核对：ForcePowerButtonOff 补丁的上下文（源文件过大）、IPMI mc info 补丁。</x:t>
         </x:is>
       </x:c>
       <x:c r="H144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CONFIG_RTC_DRV_NCT3018Y=y；rtc@6f 使用 nuvoton,nct3018y。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">上板确认 /sys/class/rtc/rtc0/name 并用 hwclock 读写验证。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；espi-peci.cfg</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="145" ht="110" customHeight="1">
-      <x:c r="A145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">待澄清</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">上电恢复策略</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Host 电源恢复</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">—</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">产品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">注释写“恢复上一次主机电源状态”，代码却把默认策略改成 AlwaysOn，两者矛盾。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">phosphor-settings-defaults-native.bbappend 将 AlwaysOff 替换为 AlwaysOn。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">确认期望策略（AlwaysOn / Restore），统一注释与代码。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J145" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">phosphor-settings-defaults-native.bbappend</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="146" ht="110" customHeight="1">
-      <x:c r="A146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">待澄清</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CFG_VER1 strap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GPIO strap</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">待定</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">EE / 硬件</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">硬件合同中有 CFG_VER1，GPIO 映射待定，本表和设备树均未命名。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">合同标记 exact_gpio_mapping_pending；设备树只命名 CFG_VER0。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">确认 CFG_VER1 的 GPIO 与用途后补充 gpio-line-names 和本表。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J146" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ceb-gnrd-hardware-contract.yaml</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="147" ht="110" customHeight="1">
-      <x:c r="A147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">待澄清</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FRU 实体 ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">motherboard FRU</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FRUID 0</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">软件 / 产品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ceb-gnrd-ipmi-fru.yaml 中保留 TODO，entityID 7 / entityInstance 1 是否符合平台 IPMI 实体定义未确认。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">使用默认值 entityID 7、entityInstance 1。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">确认后删除 TODO。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J147" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ceb-gnrd-ipmi-fru.yaml</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="148" ht="110" customHeight="1">
-      <x:c r="A148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">待澄清</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">告警 LED 服务</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BMC_SYS_ALERT_LED</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GPIOI5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">软件</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">服务通过 busctl 解析 JSON 并监听 Watchdog Timeout 信号，接口名 xyz.openbmc_project.Watchdog 与 JSON 解析格式未在目标机验证。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">已兼容 busctl 返回值外层列表和变体格式，并读取 Warning 至 HardShutdown 全部阈值接口。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">目标机验证电压越限点亮、解除熄灭、watchdog 锁存三种行为。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J148" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ceb-gnrd-alert-led.py</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="149" ht="110" customHeight="1">
-      <x:c r="A149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">待澄清</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">构建适配</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">内核 / U-Boot / IPMI / 电源控制</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">—</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="F149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">软件</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G149" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">以下内容尚未构建验证：内核 eSPI、chassis 补丁能否应用于 linux-aspeed；U-Boot 2019.04 是否识别 bootph-all；IPMI mc info 补丁已改为 libgpiod 1.x 接口；x86-power-control 的 button-passthrough 与 chassis-system-reset meson 选项是否存在。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H149" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">相关文件已就位，但没有 bitbake 构建结果。</x:t>
         </x:is>
       </x:c>
-      <x:c r="I149" s="7" t="inlineStr">
+      <x:c r="I144" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">在 Linux 构建主机执行 bitbake obmc-phosphor-image，按报错修正。</x:t>
         </x:is>
       </x:c>
-      <x:c r="J149" s="7" t="inlineStr">
+      <x:c r="J144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">linux-aspeed_%.bbappend；u-boot-aspeed-sdk_%.bbappend；phosphor-ipmi-host_%.bbappend；x86-power-control_%.bbappend</x:t>
+          <x:t xml:space="preserve">linux-aspeed_%.bbappend；ast2600-ceb-gnrd.dts；phosphor-ipmi-host_%.bbappend；x86-power-control_%.bbappend</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -4530,8 +4530,8 @@
       <x:c r="G64" s="3" t="str">
         <x:v>0x58/0x59/0x5A; input/output V and W; Linux bus i2c-7；机框内实际在位 0-2 个 PSU，地址不固定</x:v>
       </x:c>
-      <x:c r="H64" s="3" t="s">
-        <x:v>344</x:v>
+      <x:c r="H64" s="3" t="str">
+        <x:v>AST I2C8 node &amp;i2c7; pinctrl_i2c8；CRPS 不在设备树中声明，由 ceb-gnrd-psu-detect 每 5 秒检测 0x58/0x59/0x5A，仅为在位模块创建 pmbus 设备（支持热插拔）</x:v>
       </x:c>
       <x:c r="I64" s="3" t="s">
         <x:v>345</x:v>
@@ -4562,8 +4562,8 @@
       <x:c r="G65" s="3" t="str">
         <x:v>0x58/0x59/0x5A; input/output V and W; Linux bus i2c-7；机框内实际在位 0-2 个 PSU，地址不固定</x:v>
       </x:c>
-      <x:c r="H65" s="3" t="s">
-        <x:v>344</x:v>
+      <x:c r="H65" s="3" t="str">
+        <x:v>AST I2C8 node &amp;i2c7; pinctrl_i2c8；CRPS 不在设备树中声明，由 ceb-gnrd-psu-detect 每 5 秒检测 0x58/0x59/0x5A，仅为在位模块创建 pmbus 设备（支持热插拔）</x:v>
       </x:c>
       <x:c r="I65" s="3" t="s">
         <x:v>345</x:v>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -2640,7 +2640,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="2" t="str">
-        <x:v>告警灯高有效：电压 sensor 越限时点亮，电压告警解除后熄灭；BMC watchdog timeout 或 BIOS 启动 300 秒超时失败时锁存点亮，需重启解除。</x:v>
+        <x:v>告警灯高有效：电压 sensor 越限时点亮，电压告警解除后熄灭；BMC watchdog timeout 或 BIOS 启动 600 秒超时失败时锁存点亮，需重启解除。</x:v>
       </x:c>
       <x:c r="H5" s="2" t="str">
         <x:v>GPIOI5 作为 gpio-led；ceb-gnrd-alert-led 服务监听 sensor/Watchdog/BIOS boot 状态并控制输出；电压告警读取 Warning/Critical/PerformanceLoss/SoftShutdown/HardShutdown 阈值接口（ADC 的 UNR/LNR 对应 HardShutdown）。</x:v>
@@ -2768,13 +2768,13 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="G9" s="3" t="str">
-        <x:v>物理按键低有效；x86-power-control 处理按钮事件，记录 PowerButtonPressed 事件，并将输入脉冲直通 CPU power-button 输出。</x:v>
+        <x:v>物理按键低有效；仅用于检测：按下时在 SEL 和日志中记录 “Chassis Power Button Pressed”，不触发开关机，也不直通到 CPU 电源按键输出。</x:v>
       </x:c>
       <x:c r="H9" s="3" t="str">
-        <x:v>PowerButton GPIO 输入配置在 x86-power-control；button-passthrough 编译选项启用。</x:v>
+        <x:v>x86-power-control 不再配置 PowerButton，button-passthrough 未启用；ceb-gnrd-power-button-log 服务监听 BMC_POWER_BUTTON_INPUT 下降沿并写入 SEL。</x:v>
       </x:c>
       <x:c r="I9" s="3" t="str">
-        <x:v>事件处理和直通已配置；目标机验证按键电平、事件日志及脉冲。</x:v>
+        <x:v>SEL 记录已配置；目标机验证按键电平和 SEL 日志。</x:v>
       </x:c>
       <x:c r="J9" s="3" t="s">
         <x:v>18</x:v>
@@ -2800,13 +2800,13 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="G10" s="3" t="str">
-        <x:v>GPIO 高表示 BIOS boot OK；成功时不做动作。Host PWRGD 后 300 秒未拉高则锁存 BIOS boot timeout 并点亮 SYS_ALERT_LED。</x:v>
+        <x:v>GPIO 高表示 BIOS boot OK；成功时不做动作。Host PWRGD 后 600 秒未拉高则锁存 BIOS boot timeout 并点亮 SYS_ALERT_LED。</x:v>
       </x:c>
       <x:c r="H10" s="3" t="str">
         <x:v>ceb-gnrd-alert-led 服务监控 GPIOM7 和 CPU PWRGD；成功仅停止当前启动周期超时计时，失败锁存告警。</x:v>
       </x:c>
       <x:c r="I10" s="3" t="str">
-        <x:v>成功无动作、超时点灯及 PWRGD 低电平重新布防已配置；目标机验证 300 秒计时和复位条件。</x:v>
+        <x:v>成功无动作、超时点灯及 PWRGD 低电平重新布防已配置；目标机验证 600 秒计时和复位条件。</x:v>
       </x:c>
       <x:c r="J10" s="3" t="s">
         <x:v>18</x:v>
@@ -2963,7 +2963,7 @@
         <x:v>低有效 UID button；物理按键、IPMI Chassis Identify 和 Web Identify 共用 enclosure_identify LED group。</x:v>
       </x:c>
       <x:c r="H15" s="3" t="str">
-        <x:v>gpio button signals / handler 将 ID_BUTTON 映射到 identify LED group；GPIOV1 由 gpio-led-manager 控制。</x:v>
+        <x:v>phosphor-buttons 通过 gpio_defs.json（line_name BMC_UID_BUTTON_N，polarity active_low）监听按键，按下切换 enclosure_identify LED 组；GPIOV1 由 phosphor-led-manager 控制。</x:v>
       </x:c>
       <x:c r="I15" s="3" t="str">
         <x:v>按键/IPMI/Web 联动已配置；目标机验证按键行为及 identify timeout/熄灭。</x:v>
@@ -3024,13 +3024,13 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="G17" s="3" t="str">
-        <x:v>BMC chassis/host power 请求及 Web/KVM 相关主机电源操作通过标准 Host/Chassis D-Bus 状态接口触发低有效脉冲；物理电源按键按原输入脉宽直通。</x:v>
+        <x:v>BMC chassis/host power 请求及 Web/KVM 相关主机电源操作通过标准 Host/Chassis D-Bus 状态接口触发低有效脉冲；物理电源按键不直通。</x:v>
       </x:c>
       <x:c r="H17" s="3" t="str">
-        <x:v>x86-power-control PowerOut：普通按键 200 ms、强制关机 15 s；PowerOk 监测 BMC_CPU_PWRGD；button-passthrough 已启用。</x:v>
+        <x:v>x86-power-control PowerOut：普通按键 200 ms、强制关机 15 s；PowerOk 监测 BMC_CPU_PWRGD；button-passthrough 未启用。</x:v>
       </x:c>
       <x:c r="I17" s="3" t="str">
-        <x:v>板级配置已完成；目标机验证 IPMI chassis control、Web/KVM 电源操作、物理按键及 PWRGD 状态反馈。</x:v>
+        <x:v>板级配置已完成；目标机验证 IPMI chassis control、Web/KVM 电源操作及 PWRGD 状态反馈。</x:v>
       </x:c>
       <x:c r="J17" s="3" t="s">
         <x:v>18</x:v>
@@ -3143,7 +3143,7 @@
         <x:v>GPIOG6_TXD9_SD2CD#_SALT15</x:v>
       </x:c>
       <x:c r="D21" s="3" t="str">
-        <x:v>待确认（封装球位）</x:v>
+        <x:v>D21</x:v>
       </x:c>
       <x:c r="E21" s="3" t="str">
         <x:v>BMC_FRU_WP</x:v>
@@ -3698,11 +3698,11 @@
       <x:c r="G38" s="3" t="s">
         <x:v>195</x:v>
       </x:c>
-      <x:c r="H38" s="3" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="I38" s="3" t="s">
-        <x:v>197</x:v>
+      <x:c r="H38" s="3" t="str">
+        <x:v>pwm_tach fan@0；pinctrl_pwm0_default；PWM0-5 经 GPIOI6/PBI# 由 CPLD 选择归属；phosphor-pid-control 按 Entity-Manager 的 Pid 配置（控制器 SYS_FAN0，输出 PWM1）按 CPU_MAX_TEMP / DIMM_MAX_TEMP 自动调速</x:v>
+      </x:c>
+      <x:c r="I38" s="7" t="str">
+        <x:v>AST2600 PWM 节点/pinctrl 已启用；BMC 仅在 FanCtrl zone 与六路 PWM/TACH 就绪后接管；CPLD 复用动作待实板验证；PWM 控制对象名（PWM1-PWM6）待板上核对</x:v>
       </x:c>
       <x:c r="J38" s="3" t="s">
         <x:v>198</x:v>
@@ -3762,11 +3762,11 @@
       <x:c r="G40" s="3" t="s">
         <x:v>210</x:v>
       </x:c>
-      <x:c r="H40" s="3" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="I40" s="3" t="s">
-        <x:v>197</x:v>
+      <x:c r="H40" s="3" t="str">
+        <x:v>pwm_tach fan@1；pinctrl_pwm1_default；PWM0-5 经 GPIOI6/PBI# 由 CPLD 选择归属；phosphor-pid-control 按 Entity-Manager 的 Pid 配置（控制器 SYS_FAN1，输出 PWM2）按 CPU_MAX_TEMP / DIMM_MAX_TEMP 自动调速</x:v>
+      </x:c>
+      <x:c r="I40" s="7" t="str">
+        <x:v>AST2600 PWM 节点/pinctrl 已启用；BMC 仅在 FanCtrl zone 与六路 PWM/TACH 就绪后接管；CPLD 复用动作待实板验证；PWM 控制对象名（PWM1-PWM6）待板上核对</x:v>
       </x:c>
       <x:c r="J40" s="3" t="s">
         <x:v>198</x:v>
@@ -3826,11 +3826,11 @@
       <x:c r="G42" s="3" t="s">
         <x:v>222</x:v>
       </x:c>
-      <x:c r="H42" s="3" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="I42" s="3" t="s">
-        <x:v>197</x:v>
+      <x:c r="H42" s="3" t="str">
+        <x:v>pwm_tach fan@2；pinctrl_pwm2_default；PWM0-5 经 GPIOI6/PBI# 由 CPLD 选择归属；phosphor-pid-control 按 Entity-Manager 的 Pid 配置（控制器 SYS_FAN2，输出 PWM3）按 CPU_MAX_TEMP / DIMM_MAX_TEMP 自动调速</x:v>
+      </x:c>
+      <x:c r="I42" s="7" t="str">
+        <x:v>AST2600 PWM 节点/pinctrl 已启用；BMC 仅在 FanCtrl zone 与六路 PWM/TACH 就绪后接管；CPLD 复用动作待实板验证；PWM 控制对象名（PWM1-PWM6）待板上核对</x:v>
       </x:c>
       <x:c r="J42" s="3" t="s">
         <x:v>198</x:v>
@@ -3890,11 +3890,11 @@
       <x:c r="G44" s="3" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="H44" s="3" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="I44" s="3" t="s">
-        <x:v>197</x:v>
+      <x:c r="H44" s="3" t="str">
+        <x:v>pwm_tach fan@3；pinctrl_pwm3_default；PWM0-5 经 GPIOI6/PBI# 由 CPLD 选择归属；phosphor-pid-control 按 Entity-Manager 的 Pid 配置（控制器 SYS_FAN3，输出 PWM4）按 CPU_MAX_TEMP / DIMM_MAX_TEMP 自动调速</x:v>
+      </x:c>
+      <x:c r="I44" s="7" t="str">
+        <x:v>AST2600 PWM 节点/pinctrl 已启用；BMC 仅在 FanCtrl zone 与六路 PWM/TACH 就绪后接管；CPLD 复用动作待实板验证；PWM 控制对象名（PWM1-PWM6）待板上核对</x:v>
       </x:c>
       <x:c r="J44" s="3" t="s">
         <x:v>198</x:v>
@@ -3954,11 +3954,11 @@
       <x:c r="G46" s="3" t="s">
         <x:v>246</x:v>
       </x:c>
-      <x:c r="H46" s="3" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="I46" s="3" t="s">
-        <x:v>197</x:v>
+      <x:c r="H46" s="3" t="str">
+        <x:v>pwm_tach fan@4；pinctrl_pwm4_default；PWM0-5 经 GPIOI6/PBI# 由 CPLD 选择归属；phosphor-pid-control 按 Entity-Manager 的 Pid 配置（控制器 SYS_FAN4，输出 PWM5）按 CPU_MAX_TEMP / DIMM_MAX_TEMP 自动调速</x:v>
+      </x:c>
+      <x:c r="I46" s="7" t="str">
+        <x:v>AST2600 PWM 节点/pinctrl 已启用；BMC 仅在 FanCtrl zone 与六路 PWM/TACH 就绪后接管；CPLD 复用动作待实板验证；PWM 控制对象名（PWM1-PWM6）待板上核对</x:v>
       </x:c>
       <x:c r="J46" s="3" t="s">
         <x:v>198</x:v>
@@ -4018,11 +4018,11 @@
       <x:c r="G48" s="3" t="s">
         <x:v>258</x:v>
       </x:c>
-      <x:c r="H48" s="3" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="I48" s="3" t="s">
-        <x:v>197</x:v>
+      <x:c r="H48" s="3" t="str">
+        <x:v>pwm_tach fan@5；pinctrl_pwm5_default；PWM0-5 经 GPIOI6/PBI# 由 CPLD 选择归属；phosphor-pid-control 按 Entity-Manager 的 Pid 配置（控制器 SYS_FAN5，输出 PWM6）按 CPU_MAX_TEMP / DIMM_MAX_TEMP 自动调速</x:v>
+      </x:c>
+      <x:c r="I48" s="7" t="str">
+        <x:v>AST2600 PWM 节点/pinctrl 已启用；BMC 仅在 FanCtrl zone 与六路 PWM/TACH 就绪后接管；CPLD 复用动作待实板验证；PWM 控制对象名（PWM1-PWM6）待板上核对</x:v>
       </x:c>
       <x:c r="J48" s="3" t="s">
         <x:v>198</x:v>
@@ -4533,8 +4533,8 @@
       <x:c r="H64" s="3" t="str">
         <x:v>AST I2C8 node &amp;i2c7; pinctrl_i2c8；CRPS 不在设备树中声明，由 ceb-gnrd-psu-detect 每 5 秒检测 0x58/0x59/0x5A，仅为在位模块创建 pmbus 设备（支持热插拔）</x:v>
       </x:c>
-      <x:c r="I64" s="3" t="s">
-        <x:v>345</x:v>
+      <x:c r="I64" s="7" t="str">
+        <x:v>ceb-gnrd-psu-detect 按在位情况创建 pmbus 设备（0-2 个，支持热插拔）；用 STATUS_BYTE(0x78) 探测在位的方式待上板验证</x:v>
       </x:c>
       <x:c r="J64" s="3" t="s">
         <x:v>198</x:v>
@@ -4565,8 +4565,8 @@
       <x:c r="H65" s="3" t="str">
         <x:v>AST I2C8 node &amp;i2c7; pinctrl_i2c8；CRPS 不在设备树中声明，由 ceb-gnrd-psu-detect 每 5 秒检测 0x58/0x59/0x5A，仅为在位模块创建 pmbus 设备（支持热插拔）</x:v>
       </x:c>
-      <x:c r="I65" s="3" t="s">
-        <x:v>345</x:v>
+      <x:c r="I65" s="7" t="str">
+        <x:v>ceb-gnrd-psu-detect 按在位情况创建 pmbus 设备（0-2 个，支持热插拔）；用 STATUS_BYTE(0x78) 探测在位的方式待上板验证</x:v>
       </x:c>
       <x:c r="J65" s="3" t="s">
         <x:v>198</x:v>
@@ -5109,8 +5109,8 @@
       <x:c r="H82" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I82" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I82" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J82" s="3" t="s">
         <x:v>446</x:v>
@@ -5141,8 +5141,8 @@
       <x:c r="H83" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I83" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I83" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J83" s="3" t="s">
         <x:v>446</x:v>
@@ -5173,8 +5173,8 @@
       <x:c r="H84" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I84" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I84" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J84" s="3" t="s">
         <x:v>446</x:v>
@@ -5205,8 +5205,8 @@
       <x:c r="H85" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I85" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I85" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J85" s="3" t="s">
         <x:v>446</x:v>
@@ -5237,8 +5237,8 @@
       <x:c r="H86" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I86" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I86" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J86" s="3" t="s">
         <x:v>446</x:v>
@@ -5269,8 +5269,8 @@
       <x:c r="H87" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I87" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I87" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J87" s="3" t="s">
         <x:v>446</x:v>
@@ -5333,8 +5333,8 @@
       <x:c r="H89" s="3" t="s">
         <x:v>444</x:v>
       </x:c>
-      <x:c r="I89" s="3" t="s">
-        <x:v>445</x:v>
+      <x:c r="I89" s="7" t="str">
+        <x:v>配置已覆盖；构建后核对最终 DTB/pinmux，并实测 CPU eSPI。Virtual Wire 与 Flash Access channel 仍禁用；BIOS 抓包出现 SIO 访问重试和 Reserved(0E) 响应，原因待查（驱动已加日志）</x:v>
       </x:c>
       <x:c r="J89" s="3" t="s">
         <x:v>446</x:v>
@@ -5683,10 +5683,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H100" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I100" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I100" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J100" s="3" t="s">
         <x:v>567</x:v>
@@ -5715,10 +5715,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H101" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I101" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I101" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J101" s="3" t="s">
         <x:v>567</x:v>
@@ -5747,10 +5747,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H102" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I102" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I102" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J102" s="3" t="s">
         <x:v>567</x:v>
@@ -5779,10 +5779,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H103" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I103" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I103" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J103" s="3" t="s">
         <x:v>567</x:v>
@@ -5811,10 +5811,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H104" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I104" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I104" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J104" s="3" t="s">
         <x:v>567</x:v>
@@ -5843,10 +5843,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H105" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I105" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I105" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J105" s="3" t="s">
         <x:v>567</x:v>
@@ -5875,10 +5875,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H106" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I106" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I106" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J106" s="3" t="s">
         <x:v>567</x:v>
@@ -5907,10 +5907,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H107" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I107" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I107" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J107" s="3" t="s">
         <x:v>567</x:v>
@@ -5939,10 +5939,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H108" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I108" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I108" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J108" s="3" t="s">
         <x:v>567</x:v>
@@ -5971,10 +5971,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H109" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I109" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I109" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J109" s="3" t="s">
         <x:v>567</x:v>
@@ -6003,10 +6003,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H110" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I110" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I110" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J110" s="3" t="s">
         <x:v>567</x:v>
@@ -6035,10 +6035,10 @@
         <x:v>564</x:v>
       </x:c>
       <x:c r="H111" s="3" t="str">
-        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii-rxid; MDIO controller mdio1 / ethphy1</x:v>
-      </x:c>
-      <x:c r="I111" s="3" t="s">
-        <x:v>566</x:v>
+        <x:v>Linux/U-Boot eth0 -&gt; physical MAC2 (&amp;mac1); pinctrl_rgmii2_default; phy-mode rgmii; MDIO controller mdio1 / ethphy1</x:v>
+      </x:c>
+      <x:c r="I111" s="7" t="str">
+        <x:v>依原理图修正 MAC2/RGMII2 节点映射；待实测 PHY link；PHY 地址按 2 配置；PHY 不加 RGMII 延时，AST2600 SCU 延时待实测</x:v>
       </x:c>
       <x:c r="J111" s="3" t="s">
         <x:v>567</x:v>
@@ -6069,8 +6069,8 @@
       <x:c r="H112" s="3" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="I112" s="3" t="s">
-        <x:v>609</x:v>
+      <x:c r="I112" s="3" t="str">
+        <x:v>与 RGMII2 分离；PHY 地址按 2 配置（原理图备注）；PHY 复位由 CPLD 控制；实测读取 PHY ID 和链路状态</x:v>
       </x:c>
       <x:c r="J112" s="3" t="s">
         <x:v>493</x:v>
@@ -6101,8 +6101,8 @@
       <x:c r="H113" s="3" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="I113" s="3" t="s">
-        <x:v>609</x:v>
+      <x:c r="I113" s="3" t="str">
+        <x:v>与 RGMII2 分离；PHY 地址按 2 配置（原理图备注）；PHY 复位由 CPLD 控制；实测读取 PHY ID 和链路状态</x:v>
       </x:c>
       <x:c r="J113" s="3" t="s">
         <x:v>493</x:v>
@@ -6758,11 +6758,11 @@
       <x:c r="C134" s="3" t="s">
         <x:v>711</x:v>
       </x:c>
-      <x:c r="D134" s="3" t="s">
-        <x:v>712</x:v>
-      </x:c>
-      <x:c r="E134" s="3" t="s">
-        <x:v>713</x:v>
+      <x:c r="D134" s="3" t="str">
+        <x:v>AE8 (CS0) / AF8 (SCK) / AB9 (MOSI) / AD9 (MISO) / AF9 (DQ2) / AB10 (DQ3)</x:v>
+      </x:c>
+      <x:c r="E134" s="3" t="str">
+        <x:v>FLASH_SPI2_SCK / MOSI / MISO / DQ2 / DQ3（预留，未使用）</x:v>
       </x:c>
       <x:c r="F134" s="3" t="s">
         <x:v>714</x:v>
@@ -6773,8 +6773,8 @@
       <x:c r="H134" s="3" t="s">
         <x:v>716</x:v>
       </x:c>
-      <x:c r="I134" s="3" t="s">
-        <x:v>717</x:v>
+      <x:c r="I134" s="3" t="str">
+        <x:v>SPI2 仅为预留接口，本板未使用，与当前硬件定义一致</x:v>
       </x:c>
       <x:c r="J134" s="3" t="s">
         <x:v>18</x:v>
@@ -6799,14 +6799,14 @@
       <x:c r="F135" s="3" t="s">
         <x:v>442</x:v>
       </x:c>
-      <x:c r="G135" s="3" t="s">
-        <x:v>723</x:v>
+      <x:c r="G135" s="3" t="str">
+        <x:v>读取 CPU 温度及 PECI DIMM 温度，由 ceb-gnrd-temp-max 汇总为 CPU_MAX_TEMP 和 DIMM_MAX_TEMP，供风扇自动调速和 IPMI/Web 使用</x:v>
       </x:c>
       <x:c r="H135" s="3" t="s">
         <x:v>724</x:v>
       </x:c>
-      <x:c r="I135" s="3" t="s">
-        <x:v>725</x:v>
+      <x:c r="I135" s="7" t="str">
+        <x:v>已配置；汇总服务已实现，PECI 传感器的真实名字和读数需上板核对</x:v>
       </x:c>
       <x:c r="J135" s="3" t="s">
         <x:v>726</x:v>
@@ -6981,17 +6981,17 @@
       </x:c>
       <x:c r="G140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分析仪抓包显示 BIOS 反复访问 SIO 配置端口 0x2E/0x2F（写 0xA5 解锁、选择逻辑设备、读 0x20 得到 0x26），多次出现 WAIT_STATE 重试，并有 Reserved(0E) 无效响应（Slave Status Not Available）后 BIOS 重试。</x:t>
+          <x:t xml:space="preserve">分析仪抓包显示 BIOS 反复访问 SIO 配置端口 0x2E/0x2F，多次出现 WAIT_STATE 重试，并有 Reserved(0E) 无效响应后 BIOS 重试。</x:t>
         </x:is>
       </x:c>
       <x:c r="H140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMC 仅在内核驱动中置位 Peripheral SW_READY 并在 eSPI 复位后重新置位，SIO 访问完全由 AST2600 硬件完成；驱动没有错误中断处理、日志或计数，也没有 SIO 使能配置。</x:t>
+          <x:t xml:space="preserve">驱动对照 AspeedTech 官方实现补了 eSPI 复位后的控制器与 Peripheral 通道复位流程，并增加错误中断计数、告警日志和 debugfs；SIO 访问仍完全由 AST2600 硬件完成。</x:t>
         </x:is>
       </x:c>
       <x:c r="I140" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">无法从代码判断是否为硬件时序或 BMC 侧使能问题。建议在目标机读取 eSPI 控制/中断状态寄存器，确认 SIO 解码是否已使能，并让 BIOS 侧确认 0E 响应后是否重试成功。</x:t>
+          <x:t xml:space="preserve">上板后查看 dmesg | grep -i espi 和 /sys/kernel/debug/*espi*/regs 的复位次数、错误计数，把结果与抓包对照。</x:t>
         </x:is>
       </x:c>
       <x:c r="J140" s="7" t="inlineStr">
@@ -7008,17 +7008,17 @@
       </x:c>
       <x:c r="B141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">管理网口 PHY 模式</x:t>
+          <x:t xml:space="preserve">管理网口 PHY</x:t>
         </x:is>
       </x:c>
       <x:c r="C141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MAC2 / RGMII2</x:t>
+          <x:t xml:space="preserve">MAC2 / RGMII2 / RTL8211FS-CG</x:t>
         </x:is>
       </x:c>
       <x:c r="D141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RTL8211FS-CG</x:t>
+          <x:t xml:space="preserve">MDIO 地址、复位、延时</x:t>
         </x:is>
       </x:c>
       <x:c r="E141" s="7" t="inlineStr">
@@ -7028,27 +7028,27 @@
       </x:c>
       <x:c r="F141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">EE / 软件</x:t>
+          <x:t xml:space="preserve">EE / 硬件</x:t>
         </x:is>
       </x:c>
       <x:c r="G141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已将 Linux 与 U-Boot 的 phy-mode 改为 rgmii-rxid（与 AST2600 EVB 的 MAC2 一致）。PHY 地址沿用 EVB 的 reg = 0，是否与 RTL8211FS 的地址 strap 一致未确认。</x:t>
+          <x:t xml:space="preserve">PHY 地址：已确定先按原理图备注 “PHY Add = 002” 取 2（按 strap 电阻读出为 1，二者不一致，上板以实测为准）。PHY 复位 RTL8211_SYS_RSTN 由 CPLD 控制，需确认主机关机待机时已释放。strap 为 RXDLY 关闭、PHY 不加 RGMII 延时，AST2600 一侧延时待实测。</x:t>
         </x:is>
       </x:c>
       <x:c r="H141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">phy-mode = rgmii-rxid；ethphy1 reg = 0。</x:t>
+          <x:t xml:space="preserve">Linux 与 U-Boot：phy-mode = rgmii，ethphy1 reg = 2，无 reset-gpios。</x:t>
         </x:is>
       </x:c>
       <x:c r="I141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">实板验证 eth0 链路和收发；链路异常时先核对 PHY 地址和延时配置。</x:t>
+          <x:t xml:space="preserve">上板用 U-Boot mdio list / dmesg 确认实际应答地址；iperf3 与 ethtool -S 检查 CRC/错帧，必要时调整 SCU 延时。</x:t>
         </x:is>
       </x:c>
       <x:c r="J141" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts</x:t>
+          <x:t xml:space="preserve">原理图 PHY strap 页；aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7085,7 +7085,7 @@
       </x:c>
       <x:c r="G142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">内核 rtc-nct3018y 的 compatible 和 binding 只写 NCT3018Y，没有提到 NCT3015Y。仓库内其他项目（如 nvidia）同样只启用 CONFIG_RTC_DRV_NCT3018Y，没有 NCT3015Y 的专门节点可参照。</x:t>
+          <x:t xml:space="preserve">内核 rtc-nct3018y 的 compatible 和 binding 只写 NCT3018Y，没有提到 NCT3015Y，寄存器兼容性未在目标机验证。</x:t>
         </x:is>
       </x:c>
       <x:c r="H142" s="7" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </x:c>
       <x:c r="G143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Watchdog 信号的接口名 xyz.openbmc_project.Watchdog 和成员 Timeout 已对照 phosphor-sel-logger 源码，与脚本一致；busctl 的 JSON 返回格式仍按文档处理，未在目标机验证。</x:t>
+          <x:t xml:space="preserve">Watchdog 信号的接口名已对照 phosphor-sel-logger 源码一致；busctl 的 JSON 返回格式仍按文档处理，未在目标机验证。BIOS Boot OK 超时已改为 600 秒。</x:t>
         </x:is>
       </x:c>
       <x:c r="H143" s="7" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </x:c>
       <x:c r="I143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">目标机验证电压越限点亮、解除熄灭、watchdog 锁存三种行为。</x:t>
+          <x:t xml:space="preserve">目标机验证电压越限点亮、解除熄灭、watchdog 锁存、BIOS 启动超时 4 种行为。</x:t>
         </x:is>
       </x:c>
       <x:c r="J143" s="7" t="inlineStr">
@@ -7164,47 +7164,255 @@
       </x:c>
       <x:c r="B144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">构建适配</x:t>
+          <x:t xml:space="preserve">风扇控制配置</x:t>
         </x:is>
       </x:c>
       <x:c r="C144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">内核 / U-Boot / IPMI / 电源控制</x:t>
+          <x:t xml:space="preserve">6 路风扇 / 网页 Fan control</x:t>
         </x:is>
       </x:c>
       <x:c r="D144" s="7" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">PWM0-5、TACH0-5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件 / 硬件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning/Critical/HardShutdown）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-pid-control + Entity-Manager Pid 配置；ceb-gnrd-temp-max 汇总 PECI 传感器并发布 CPU_MAX_TEMP / DIMM_MAX_TEMP；ceb-gnrd-fan-settings 服务提供“BMC 重启后保留设置”（保存到 /var/lib/ceb-gnrd，通过 bmcweb 的 dbus-rest 访问）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上板核对 /xyz/openbmc_project/control/fanpwm/ 下对象名；用 journalctl -u ceb-gnrd-temp-max 核对识别出的 CPU/DIMM 传感器名；确认两条阶梯曲线（CPU 40-90℃、DIMM 40-80℃）；验证保存/恢复和断电重启后的行为。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J144" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd.json；ceb-gnrd-fan-settings.py；0003 网页补丁</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="125" customHeight="1">
+      <x:c r="A145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PSU 在位检测</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">I2C8 / 0x58 0x59 0x5A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CRPS PMBus</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件 / 硬件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-psu-detect 每 5 秒用 STATUS_BYTE(0x78) 探测在位模块，仅为在位的创建 pmbus 设备；个别 PSU 是否应答该命令未在实物上验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">设备树不再声明 pmbus 节点；Entity-Manager 仍配置 3 个地址。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上板用 1 个和 2 个 PSU 各验证一次，查看 journalctl -u ceb-gnrd-psu-detect。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J145" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-psu-detect.sh；aspeed-ceb-gnrd.dts</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="125" customHeight="1">
+      <x:c r="A146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">mc info 与 BMC 状态</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IPMI Get Device ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Device Available / Firmware Revision</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Manufacturer ID 已按用户给定值 0x1A03（6659）；Device Available 取决于 BMC 状态是否为 Ready，虚拟机里可能因 KCS 等服务失败而显示 no；Firmware Revision 来自 DISTRO_VERSION=1.0.0。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dev_id.json：id 32，revision 0x82，prod_id 3346，addn_dev_support 0x8F；ipmitool 补丁显示产品名 CEB-GNR-D 与公司名 CTOPAI。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">确认正式 IANA 编号和版本号规则；上板检查 obmcutil state。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J146" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dev_id.json；ipmitool_%.bbappend；ceb-gnrd.conf</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="125" customHeight="1">
+      <x:c r="A147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IPMI 传感器暴露</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ipmitool sensor / Web 传感器</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ADC、温度、风扇、CPU、DIMM</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">产品 / 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已启用 dynamic-sensors 和 hybrid-sensors，ADC 电压、温度、风扇、CPU_MAX_TEMP、DIMM_MAX_TEMP 会出现在 IPMI；动态传感器改用 sel-logger 的 SEL 文件，SEL 行为变化未在目标机验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已去掉默认表里的逐核 CPU、DIMM、DeratingFactor；网页传感器页走 Redfish，不受影响。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上板核对 ipmitool sensor / sdr 列表和 SEL（含电源按键 SEL）是否正常。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J147" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-ipmi-sensor-inventory-native；phosphor-ipmi-host_%.bbappend</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="125" customHeight="1">
+      <x:c r="A148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">构建与验证状态</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">内核 / U-Boot / 网页 / IPMI / 电源控制</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D148" s="7" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
-      <x:c r="E144" s="7" t="inlineStr">
+      <x:c r="E148" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F144" s="7" t="inlineStr">
+      <x:c r="F148" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">软件</x:t>
         </x:is>
       </x:c>
-      <x:c r="G144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">已核对：x86-power-control 存在 button-passthrough 与 chassis-system-reset 选项；内核 Kconfig、hwmon Makefile、g6 dtsi 的补丁上下文与 SRCREV 一致，eSPI 的 Makefile 行改由 bbappend 追加；U-Boot 设备树已删除不存在的 &amp;mdio2 和 fwspid/fwqspi pinctrl 引用，bootph-all 改为 u-boot,dm-pre-reloc。仍未核对：ForcePowerButtonOff 补丁的上下文（源文件过大）、IPMI mc info 补丁。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">相关文件已就位，但没有 bitbake 构建结果。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">在 Linux 构建主机执行 bitbake obmc-phosphor-image，按报错修正。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J144" s="7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">linux-aspeed_%.bbappend；ast2600-ceb-gnrd.dts；phosphor-ipmi-host_%.bbappend；x86-power-control_%.bbappend</x:t>
+      <x:c r="G148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">网页补丁 0003-0008 已逐个对真实源码校验可打上；ForcePowerButtonOff、IPMI mc info 补丁带 fuzz，已将 patch-fuzz 降为警告；整机完整构建和上板验证尚未完成。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">相关文件已就位。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">在 Linux 构建主机执行 bitbake obmc-phosphor-image，按报错修正，再上板按本表红字项逐一验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J148" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">linux-aspeed_%.bbappend；webui-vue_%.bbappend；phosphor-ipmi-host_%.bbappend；x86-power-control_%.bbappend</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7189,7 +7189,7 @@
       </x:c>
       <x:c r="G144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning/Critical/HardShutdown）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
+          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning/Critical/HardShutdown）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。全速保护只看温度：CPU 或 DIMM 温度读不到（host 已开机）时 ceb-gnrd-temp-max 发布 127 ℃，曲线给 100%；Zone 的 FailSafePercent 设为 30，所以风扇读到几个都不会触发全速。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
         </x:is>
       </x:c>
       <x:c r="H144" s="7" t="inlineStr">

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -5359,14 +5359,14 @@
       <x:c r="F90" s="3" t="s">
         <x:v>489</x:v>
       </x:c>
-      <x:c r="G90" s="3" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="H90" s="3" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="I90" s="3" t="s">
-        <x:v>492</x:v>
+      <x:c r="G90" s="7" t="str">
+        <x:v>BMC 到 Host CPU 的 SOL 串口发送；本板 SOL 只能接收，此信号不用，TXD3 不复用</x:v>
+      </x:c>
+      <x:c r="H90" s="7" t="str">
+        <x:v>&amp;uart3 status okay; TXD3 not muxed (receive-only SOL)</x:v>
+      </x:c>
+      <x:c r="I90" s="7" t="str">
+        <x:v>未启用（SOL 只读，不向主机发送）</x:v>
       </x:c>
       <x:c r="J90" s="3" t="s">
         <x:v>493</x:v>
@@ -5394,8 +5394,8 @@
       <x:c r="G91" s="3" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="H91" s="3" t="s">
-        <x:v>499</x:v>
+      <x:c r="H91" s="7" t="str">
+        <x:v>&amp;uart3 status okay; pinctrl_rxd3_default only; obmc-console server.ttyS2.conf baud 115200</x:v>
       </x:c>
       <x:c r="I91" s="3" t="s">
         <x:v>492</x:v>
@@ -7090,12 +7090,12 @@
       </x:c>
       <x:c r="H142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">沿用 nuvoton,nct3018y 与 CONFIG_RTC_DRV_NCT3018Y=y。</x:t>
+          <x:t xml:space="preserve">沿用 nuvoton,nct3018y 与 CONFIG_RTC_DRV_NCT3018Y=y；关闭 AST2600 内部 RTC（无电池），使 NCT3015Y 成为 rtc0，内核 HCTOSYS 在开机时设置系统时间，另有 ceb-gnrd-rtc-sync 服务兜底。BMC 系统时间和 SEL 时间默认来自 RTC。</x:t>
         </x:is>
       </x:c>
       <x:c r="I142" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上板确认 /sys/class/rtc/rtc0/name 并用 hwclock 读写验证。</x:t>
+          <x:t xml:space="preserve">上板确认 /sys/class/rtc/rtc0/name 是 NCT3018Y；断电重启后 date 与 ipmitool sel time get 应保持 RTC 的时间；用 hwclock 读写验证。</x:t>
         </x:is>
       </x:c>
       <x:c r="J142" s="7" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </x:c>
       <x:c r="H143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已兼容 busctl 返回值外层列表和变体格式，并读取 Warning 至 HardShutdown 全部阈值接口。</x:t>
+          <x:t xml:space="preserve">已兼容 busctl 返回值外层列表和变体格式，并读取 Warning 至 HardShutdown 全部阈值接口。新增温度告警：任一温度传感器的 Critical 或 HardShutdown 上限告警（CriticalAlarmHigh / HardShutdownAlarmHigh）置位就点亮，解除后熄灭；电压和温度告警自动解除，watchdog 超时和 BIOS 启动超时锁存到 BMC 重启。4 种告警共用一个灯，任一存在就亮。所有告警都写 SEL：电压/温度由 sel-logger 的阈值监视记录（CPU/DIMM 汇总服务发 ThresholdAsserted 信号；sel-logger 加补丁支持 HardShutdown=不可恢复级别），watchdog 超时由 sel-logger 的 watchdog 监视记录，BIOS 启动失败由本服务调用 IpmiSelAdd 记录。SEL 为 rollover：最多保留约 2000 条，满了自动丢弃最老的（ceb-gnrd-sel-rollover，可能在整理瞬间丢 1 条新记录）。</x:t>
         </x:is>
       </x:c>
       <x:c r="I143" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">目标机验证电压越限点亮、解除熄灭、watchdog 锁存、BIOS 启动超时 4 种行为。</x:t>
+          <x:t xml:space="preserve">目标机验证电压越限、温度超 Upper Critical（点亮、解除熄灭）、watchdog 锁存、BIOS 启动超时（需重启 BMC 才熄灭）4 种行为，以及多种告警同时存在时灯的状态；每种告警在 ipmitool sel list 里都能看到（含解除事件）；SEL 超过 2100 条后确认最老的被删除、记录号继续递增。</x:t>
         </x:is>
       </x:c>
       <x:c r="J143" s="7" t="inlineStr">
@@ -7246,12 +7246,12 @@
       </x:c>
       <x:c r="H145" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">设备树不再声明 pmbus 节点；Entity-Manager 仍配置 3 个地址。</x:t>
+          <x:t xml:space="preserve">设备树不再声明 pmbus 节点；Entity-Manager 仍配置 3 个地址；每个模块的传感器有输入/输出电压、输入/输出功率和 PSUn_Temp（pmbus 的 temp2，按用户指定）。</x:t>
         </x:is>
       </x:c>
       <x:c r="I145" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上板用 1 个和 2 个 PSU 各验证一次，查看 journalctl -u ceb-gnrd-psu-detect。</x:t>
+          <x:t xml:space="preserve">上板用 1 个和 2 个 PSU 各验证一次，查看 journalctl -u ceb-gnrd-psu-detect；并核对 temp2 是否存在、是否真是电源温度（用户指定取 temp2）。</x:t>
         </x:is>
       </x:c>
       <x:c r="J145" s="7" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </x:c>
       <x:c r="G146" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Manufacturer ID 已按用户给定值 0x1A03（6659）；Device Available 取决于 BMC 状态是否为 Ready，虚拟机里可能因 KCS 等服务失败而显示 no；Firmware Revision 来自 DISTRO_VERSION=1.0.0。</x:t>
+          <x:t xml:space="preserve">Manufacturer ID 已按用户给定值 0x1A03（6659）；Device Available 取决于 BMC 状态是否为 Ready，虚拟机里可能因 KCS 等服务失败而显示 no；Firmware Revision 来自 DISTRO_VERSION=1.0.0。主机到 BMC 的 IPMI 走 KCS3（I/O 端口 0xCA2/0xCA3）：设备树已补 aspeed,lpc-io-reg = &lt;0xca2&gt;（内核驱动必须有该属性，否则 KCS 不会起来），未配 SerIRQ（eSPI 不用虚拟线，主机轮询状态寄存器）；需要 eSPI 外设通道就绪并且主机 BIOS 把 KCS 端口设为 0xCA2 才通，上板验证。</x:t>
         </x:is>
       </x:c>
       <x:c r="H146" s="7" t="inlineStr">

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7416,6 +7416,318 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="149" ht="125" customHeight="1">
+      <x:c r="A149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">U-Boot 网络启动与 netupdate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bootcmd / netupdate / serverip</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AST2600 MAC2 + RTL8211FS（U-Boot 里只用该口）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">默认先从 TFTP 服务器 192.168.185.84 取 fitImage，失败回退本地 flash；run netupdate 用 TFTP 更新闪存里的内核和 rofs（不动 U-Boot、环境、rwfs）。U-Boot 环境存在闪存里，旧环境会盖住新默认值；ethaddr 不保存就是随机 MAC。虚拟机里 TFTP 服务器是 192.168.185.1（QEMU 的 tftp= 选项），物理板子是 .84；虚拟机里 PHY 和 mii 是模拟的。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-netboot.cfg 写 CONFIG_BOOTCOMMAND；ceb-gnrd-env.h 加 netupdate 变量，由 u-boot bbappend 的 sed 接入 evb_ast2600a1_spl.h；默认 IP 改成与 Linux eth0 一致；U-Boot 设备树禁用 NC-SI 口（启用会崩溃）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">烧入新 U-Boot 后在 U-Boot 里 env default -a; setenv ethaddr ...; saveenv；日志里看 TFTP from server 192.168.185.84；run netupdate 后 reset；上板验证 RGMII 延时（100M 通而 1000M 不通就是延时问题）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J149" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">quick-start.md 第四章 4；ceb-gnrd-netboot.cfg；ceb-gnrd-env.h；u-boot-aspeed-sdk_%.bbappend；ast2600-ceb-gnrd.dts</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="125" customHeight="1">
+      <x:c r="A150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主机 KCS 通道</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">kcs3 / ipmi-kcs3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AST2600 LPC KCS3，I/O 端口 0xCA2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">硬件 + 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">内核 KCS 驱动没有 aspeed,lpc-io-reg 属性就不会 probe；已补 &lt;0xca2&gt;，未配 SerIRQ（eSPI 不用虚拟线，主机轮询状态寄存器）。要 eSPI 外设通道就绪并且主机 BIOS 把 KCS 端口设为 0xCA2 才通。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts 的 &amp;kcs3；phosphor-ipmi-kcs（ipmi-kcs3）；channel_config.json 的 15 号通道。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC：ls /dev/ipmi-kcs3，journalctl -u phosphor-ipmi-kcs@ipmi-kcs3；主机：ipmitool -I open mc info；同时看 eSPI 日志。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J150" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；espi-peci.cfg；phosphor-ipmi-kcs 配置</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="125" customHeight="1">
+      <x:c r="A151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NC-SI 网口（eth1）拉起与重试</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">eth1 / ceb-gnrd-ncsi</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AST2600 MAC3 + Intel E810（无待机供电）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">E810 在主机关机时没有供电，主机上电后也不一定立刻就绪；内核 NC-SI 探测失败后不会自动重试。重试间隔 30 秒、最多 3 次是估计值。U-Boot 里该口禁用。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">manage-ncsi-link.sh 监视机箱电源，上电后拉起 eth1；30 秒内没有链路就 down/up 重试，每 30 秒一次最多 3 次；关机时关闭；systemd-networkd 用 ActivationPolicy=manual，DHCP=ipv4。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主机上电后 ip -br addr show eth1，journalctl -t ceb-gnrd-ncsi 看有没有重试，实测 E810 多久就绪后调整间隔和次数。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J151" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">manage-ncsi-link.sh；ceb-gnrd-ncsi.service；20-ceb-gnrd-eth1-ncsi.network；ast2600-ceb-gnrd.dts</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="125" customHeight="1">
+      <x:c r="A152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SEL 记录与 rollover</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ipmi_sel / sel-logger</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">电压、温度（含 CPU/DIMM 汇总、不可恢复级别）、watchdog 超时、BIOS 启动失败、电源按键都写 SEL；SEL 为 rollover（约 2000 条，满了丢最老的，整理瞬间可能丢 1 条新记录）；/var/log 是否掉电保留未核实。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-temp-max 发 ThresholdAsserted 信号；sel-logger 补丁支持 HardShutdown 级别；告警灯服务对 BIOS 启动失败调用 IpmiSelAdd；ceb-gnrd-sel-rollover 服务裁剪 /var/log/ipmi_sel。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">制造各种越限，ipmitool sel list 看事件和解除事件；塞满 2100 条后确认最老的被删、记录号继续递增。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J152" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-temp-max.py；ceb-gnrd-alert-led.py；phosphor-sel-logger_%.bbappend 和补丁；ceb-gnrd-sel-rollover.sh</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="125" customHeight="1">
+      <x:c r="A153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">网页补丁和 bmcweb 选项</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">webui 0009-0011；redfish-dump-log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">转储页需要 bmcweb 的 redfish-dump-log，配方默认不编译该路由，之前转储页没有后端，已在 bmcweb bbappend 里启用。概览页电源卡片、固件页备份镜像卡片、System dump 选项已移除。固件页 BIOS 卡片的运行版本显示 --（暂不处理）。虚拟媒体只支持浏览器读镜像，外部服务器模式需要停止维护的 virtual-media 服务，不提供。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0009 去掉概览页电源信息卡片；0010 去掉备份镜像卡片；0011 转储类型只留 BMC dump；bmcweb_%.bbappend 加 redfish-dump-log。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">网页逐页点开，看有没有 -- 或报错；转储页点 Initiate dump 应能生成并下载。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J153" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">webui/files/0009-0011 补丁；webui-vue_%.bbappend；bmcweb_%.bbappend</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="125" customHeight="1">
+      <x:c r="A154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DCMI 与 IPMI 常规命令</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">dcmi / power_reading.json / dcmi_sensors.json</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DCMI 电源读数和温度读数没有配置（路径为空、传感器数组为空），ipmitool dcmi power reading / get_temp_reading 返回无内容；其他常规命令（mc、chassis、sdr、sel、fru、lan、user、sol）都有对应后端。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">无需改动；若要支持 DCMI，需要加一个总功率传感器，并在 dcmi_sensors.json 里映射进风、主板、CPU 温度。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ipmitool dcmi power reading 应报不支持；其余命令上板逐个验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J154" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-ipmi-config（默认）；ceb-gnrd-ipmi-sensors/config.yaml</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7189,7 +7189,7 @@
       </x:c>
       <x:c r="G144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning/Critical/HardShutdown）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。全速保护只看温度：CPU 或 DIMM 温度读不到（host 已开机）时 ceb-gnrd-temp-max 发布 127 ℃，曲线给 100%；Zone 的 FailSafePercent 设为 30，所以风扇读到几个都不会触发全速。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
+          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning/Critical/HardShutdown）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。全速保护只看温度：CPU 或 DIMM 温度读不到（host 已开机）时 ceb-gnrd-temp-max 发布 70 ℃，两条曲线在 70 ℃ 都是 60%（读不到时风扇 60%）；Zone 的 FailSafePercent 设为 30，所以风扇读到几个都不会触发全速。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
         </x:is>
       </x:c>
       <x:c r="H144" s="7" t="inlineStr">

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -3183,8 +3183,8 @@
       <x:c r="F22" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G22" s="3" t="s">
-        <x:v>109</x:v>
+      <x:c r="G22" s="7" t="str">
+        <x:v>P12V_SYS 12 V 标称；ScaleFactor 11；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H22" s="3" t="str">
         <x:v>adc0 ch0 (pad ADC0) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3215,8 +3215,8 @@
       <x:c r="F23" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G23" s="3" t="s">
-        <x:v>117</x:v>
+      <x:c r="G23" s="7" t="str">
+        <x:v>P5V0_SYS 5 V 标称；ScaleFactor 11；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H23" s="3" t="str">
         <x:v>adc0 ch1 (pad ADC1) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3247,8 +3247,8 @@
       <x:c r="F24" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G24" s="3" t="s">
-        <x:v>122</x:v>
+      <x:c r="G24" s="7" t="str">
+        <x:v>P3V3_SYS 3.3 V 标称；ScaleFactor 2；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H24" s="3" t="str">
         <x:v>adc0 ch2 (pad ADC2) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3279,8 +3279,8 @@
       <x:c r="F25" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G25" s="3" t="s">
-        <x:v>127</x:v>
+      <x:c r="G25" s="7" t="str">
+        <x:v>PVCCIN_CPU 1.8 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H25" s="3" t="str">
         <x:v>adc0 ch3 (pad ADC3) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3311,8 +3311,8 @@
       <x:c r="F26" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G26" s="3" t="s">
-        <x:v>132</x:v>
+      <x:c r="G26" s="7" t="str">
+        <x:v>PVNN_NAC_CPU 0.9 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H26" s="3" t="str">
         <x:v>adc0 ch4 (pad ADC4) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3343,8 +3343,8 @@
       <x:c r="F27" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G27" s="3" t="s">
-        <x:v>137</x:v>
+      <x:c r="G27" s="7" t="str">
+        <x:v>PVCCD0_HV_CPU 1.13 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H27" s="3" t="str">
         <x:v>adc0 ch5 (pad ADC5) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3375,8 +3375,8 @@
       <x:c r="F28" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G28" s="3" t="s">
-        <x:v>142</x:v>
+      <x:c r="G28" s="7" t="str">
+        <x:v>PVCCINF_CPU 0.85 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H28" s="3" t="str">
         <x:v>adc0 ch6 (pad ADC6) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3407,8 +3407,8 @@
       <x:c r="F29" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G29" s="3" t="s">
-        <x:v>147</x:v>
+      <x:c r="G29" s="7" t="str">
+        <x:v>PVNN_MAIN_CPU 1 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H29" s="3" t="str">
         <x:v>adc0 ch7 (pad ADC7) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3439,8 +3439,8 @@
       <x:c r="F30" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G30" s="3" t="s">
-        <x:v>152</x:v>
+      <x:c r="G30" s="7" t="str">
+        <x:v>PVCCFA_EHV_CPU 1.8 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H30" s="3" t="str">
         <x:v>adc1 ch0 (pad ADC8) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3471,8 +3471,8 @@
       <x:c r="F31" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G31" s="3" t="s">
-        <x:v>157</x:v>
+      <x:c r="G31" s="7" t="str">
+        <x:v>PVCCD1_HV_CPU 1.13 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H31" s="3" t="str">
         <x:v>adc1 ch1 (pad ADC9) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3503,8 +3503,8 @@
       <x:c r="F32" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G32" s="3" t="s">
-        <x:v>162</x:v>
+      <x:c r="G32" s="7" t="str">
+        <x:v>PVCCINF_EHV_FIVRA_CPU 1.8 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H32" s="3" t="str">
         <x:v>adc1 ch2 (pad ADC10) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3535,8 +3535,8 @@
       <x:c r="F33" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G33" s="3" t="s">
-        <x:v>167</x:v>
+      <x:c r="G33" s="7" t="str">
+        <x:v>P3V3_STBY 3.3 V 标称；ScaleFactor 2；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H33" s="3" t="str">
         <x:v>adc1 ch3 (pad ADC11) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3567,8 +3567,8 @@
       <x:c r="F34" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G34" s="3" t="s">
-        <x:v>172</x:v>
+      <x:c r="G34" s="7" t="str">
+        <x:v>P1V8_STBY 1.8 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H34" s="3" t="str">
         <x:v>adc1 ch4 (pad ADC12) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3599,8 +3599,8 @@
       <x:c r="F35" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G35" s="3" t="s">
-        <x:v>177</x:v>
+      <x:c r="G35" s="7" t="str">
+        <x:v>P1V2_STBY 1.2 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H35" s="3" t="str">
         <x:v>adc1 ch5 (pad ADC13) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>
@@ -3631,8 +3631,8 @@
       <x:c r="F36" s="3" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G36" s="3" t="s">
-        <x:v>182</x:v>
+      <x:c r="G36" s="7" t="str">
+        <x:v>P1V0_STBY 1 V 标称；ScaleFactor 1；UC/LC ±15%（阈值级别用 Critical，这样 ipmitool 能显示；规格表写的是 UNR/LNR）</x:v>
       </x:c>
       <x:c r="H36" s="3" t="str">
         <x:v>adc1 ch6 (pad ADC14) + iio-hwmon；Vref 内部 2.5 V（aspeed,int-vref-microvolt）；Entity-Manager ADC sensor</x:v>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7293,7 +7293,7 @@
       </x:c>
       <x:c r="G146" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Manufacturer ID 已按用户给定值 0x1A03（6659）；Device Available 取决于 BMC 状态是否为 Ready，虚拟机里可能因 KCS 等服务失败而显示 no；Firmware Revision 来自 DISTRO_VERSION=1.0.0。主机到 BMC 的 IPMI 走 KCS3（I/O 端口 0xCA2/0xCA3）：设备树已补 aspeed,lpc-io-reg = &lt;0xca2&gt;（内核驱动必须有该属性，否则 KCS 不会起来），未配 SerIRQ（eSPI 不用虚拟线，主机轮询状态寄存器）；需要 eSPI 外设通道就绪并且主机 BIOS 把 KCS 端口设为 0xCA2 才通，上板验证。</x:t>
+          <x:t xml:space="preserve">Manufacturer ID 已按用户给定值 0x1A03（6659）；Device Available 取决于 BMC 状态是否为 Ready，虚拟机里可能因 KCS 等服务失败而显示 no；Firmware Revision 来自 DISTRO_VERSION=2.0.0（固件版本从 2.0 开始，ipmitool 显示 2.00）。主机到 BMC 的 IPMI 走 KCS3（I/O 端口 0xCA2/0xCA3）：设备树已补 aspeed,lpc-io-reg = &lt;0xca2&gt;（内核驱动必须有该属性，否则 KCS 不会起来），未配 SerIRQ（eSPI 不用虚拟线，主机轮询状态寄存器）；需要 eSPI 外设通道就绪并且主机 BIOS 把 KCS 端口设为 0xCA2 才通，上板验证。</x:t>
         </x:is>
       </x:c>
       <x:c r="H146" s="7" t="inlineStr">

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7189,7 +7189,7 @@
       </x:c>
       <x:c r="G144" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning/Critical/HardShutdown）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。全速保护只看温度：CPU 或 DIMM 温度读不到（host 已开机）时 ceb-gnrd-temp-max 发布 70 ℃，两条曲线在 70 ℃ 都是 60%（读不到时风扇 60%）；Zone 的 FailSafePercent 设为 30，所以风扇读到几个都不会触发全速。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
+          <x:t xml:space="preserve">6 个风扇各一个 Pid 控制器（SYS_FAN0-5，输出 PWM1-PWM6），1 个 Zone；自动调速只看 CPU_MAX_TEMP 和 DIMM_MAX_TEMP 两条阶梯曲线（默认曲线是暂定值，待确认）。告警阈值按规格表（只设上限）：CPU_MAX_TEMP 90/98/105 ℃，DIMM_MAX_TEMP 80/85/95 ℃，分别对应 UNC/UC/UNR（Warning / Critical / 私有接口 CebGnrd.Threshold.NonRecoverable；不用 HardShutdown，BMC 不因阈值自动关机，镜像里去掉了会据此关机的 phosphor-fan sensor-monitor）；表中括号顺序写的是 UNR,UC,UNC，这里按数值由小到大理解，待确认。全速保护只看温度：CPU 或 DIMM 温度读不到（host 已开机）时 ceb-gnrd-temp-max 发布 70 ℃，两条曲线在 70 ℃ 都是 60%（读不到时风扇 60%）；Zone 的 FailSafePercent 设为 30，所以风扇读到几个都不会触发全速。6 个风扇都不设转速告警阈值（实际接几个风扇不确定，没接的风扇读 0 RPM，不产生 SEL、日志或告警灯）。PWM 控制对象名（PWM1-PWM6）是软件对象名，按 dbus-sensors 源码推断，未在板上核对。CPU/DIMM 传感器按名字规则识别（含 dimm 的算 DIMM，排除 DTS、Tcontrol 等），真实名字上板后核对。</x:t>
         </x:is>
       </x:c>
       <x:c r="H144" s="7" t="inlineStr">
@@ -7449,17 +7449,17 @@
       </x:c>
       <x:c r="G149" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">默认先从 TFTP 服务器 192.168.185.84 取 fitImage，失败回退本地 flash；run netupdate 用 TFTP 更新闪存里的内核和 rofs（不动 U-Boot、环境、rwfs）。U-Boot 环境存在闪存里，旧环境会盖住新默认值；ethaddr 不保存就是随机 MAC。虚拟机里 TFTP 服务器是 192.168.185.1（QEMU 的 tftp= 选项），物理板子是 .84；虚拟机里 PHY 和 mii 是模拟的。</x:t>
+          <x:t xml:space="preserve">U-Boot 固定从本地 SPI 闪存启动（bootcmd = run bootspi），不自动走 TFTP；TFTP 只用于手动网络启动调试和 run netupdate 用 TFTP 更新闪存里的内核和 rofs（不动 U-Boot、环境、rwfs）。U-Boot 环境存在闪存里，旧环境会盖住新默认值；ethaddr 不保存就是随机 MAC。虚拟机里 TFTP 服务器是 192.168.185.1（QEMU 的 tftp= 选项），物理板子是 .84；虚拟机里 PHY 和 mii 是模拟的。</x:t>
         </x:is>
       </x:c>
       <x:c r="H149" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ceb-gnrd-netboot.cfg 写 CONFIG_BOOTCOMMAND；ceb-gnrd-env.h 加 netupdate 变量，由 u-boot bbappend 的 sed 接入 evb_ast2600a1_spl.h；默认 IP 改成与 Linux eth0 一致；U-Boot 设备树禁用 NC-SI 口（启用会崩溃）。</x:t>
+          <x:t xml:space="preserve">ceb-gnrd-env.h 加 netupdate 变量，由 u-boot bbappend 的 sed 接入 evb_ast2600a1_spl.h；默认 IP 改成与 Linux eth0 一致；U-Boot 设备树禁用 NC-SI 口（启用会崩溃）。</x:t>
         </x:is>
       </x:c>
       <x:c r="I149" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">烧入新 U-Boot 后在 U-Boot 里 env default -a; setenv ethaddr ...; saveenv；日志里看 TFTP from server 192.168.185.84；run netupdate 后 reset；上板验证 RGMII 延时（100M 通而 1000M 不通就是延时问题）。</x:t>
+          <x:t xml:space="preserve">烧入新 U-Boot 后在 U-Boot 里 env default -a; setenv ethaddr ...; saveenv；确认 printenv bootcmd 是 run bootspi（旧环境里保存过带 tftpboot 的 bootcmd 会盖住默认值）；run netupdate 后 reset；上板验证 RGMII 延时（100M 通而 1000M 不通就是延时问题）。</x:t>
         </x:is>
       </x:c>
       <x:c r="J149" s="7" t="inlineStr">
@@ -7725,6 +7725,58 @@
       <x:c r="J154" s="7" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">phosphor-ipmi-config（默认）；ceb-gnrd-ipmi-sensors/config.yaml</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="125" customHeight="1">
+      <x:c r="A155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">风扇 OEM 命令（netfn 0x30）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-ipmi-fan / fan_oem.cpp / ceb-gnrd-fan-settings.py</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新增两条 OEM 命令：0x30 0x01 读取每个风扇的模式、占空比、转速；0x30 0x02 设置（风扇 0-5 或 0xFF、模式、占空比、是否保留）。网页的“最低风扇转速”已去掉，自适应固定为 30%–100%；网页命令框给出对应 ipmitool 命令。C++ 库没有编译、没有验证。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需要重新编译；确认 libcebgnrdfancmd.so 被 host-ipmid 和 net-ipmid 加载，白名单（0x30:0x01/0x02）生效。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ipmitool raw 0x30 0x01 返回 25 字节；ipmitool raw 0x30 0x02 0xFF 0x01 0x3C 0x01 后再读，6 个风扇均为模式 1、占空比 60；网页风扇下拉框里没有 @odata 项。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J155" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-ipmi-fan.bb；ceb-gnrd-ipmi-whitelist.conf；0003-ceb-gnrd-add-fan-control-page.patch</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7780,6 +7780,370 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="156" ht="125" customHeight="1">
+      <x:c r="A156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">风扇设置写 Entity-Manager 报 InvalidArgs</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-fan-settings.py / ceb-gnrd.json（Pid 改名 Fan&lt;n&gt; Control）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对 Pid 的 OutLimitMin/Max 写入时值已被改掉，但 Entity-Manager 返回 InvalidArgs，日志里没有它的报错，原因没有查清。网页保存和 ipmitool raw 0x30 0x02 曾因此失败。已让服务回读确认；网页改为分三步调用不带参数的方法（bmcweb 的 D-Bus REST 在此版本不能传标量参数）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">原因待查（可能与 Entity-Manager 保存自己的 JSON 副本有关）；目前回读确认可以绕过。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QEMU 里 ceb-gnrd-check 的风扇项全部 PASS；网页选单个风扇保存后 ipmitool raw 0x30 0x01 读回一致。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J156" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-fan-settings.py；0003-ceb-gnrd-add-fan-control-page.patch</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="125" customHeight="1">
+      <x:c r="A157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">开机后一分钟内 ipmitool sensor 只有 2 个</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-ipmi-host drop-in 10-ceb-gnrd-wait-sensors.conf</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ipmid 在传感器阈值接口出现前去读会失败，只剩静态传感器。已让 ipmid 启动前最多等 90 秒，直到传感器数量连续 8 秒不变；代价是开机后约一分钟 ipmitool 不可用。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上物理板后主机 BIOS 很早就用 KCS，要确认这个延迟是否可接受，必要时缩短上限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">开机后立即运行 ipmitool sensor 应已有约 20 行；systemd-analyze blame 看 phosphor-ipmi-host 耗时。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J157" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-ipmi-host_%.bbappend；files/10-ceb-gnrd-wait-sensors.conf</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="125" customHeight="1">
+      <x:c r="A158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Redfish FirmwareVersion 为空 / 网页 BMC 版本 --</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bmcweb_%.bbappend</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bmcweb 默认到 /software/bmc/functional 找 BMC 版本，经典 phosphor-image-updater 发布在 /software/functional。已设 -Dredfish-updateservice-use-dbus=disabled，同时固件上传走 /tmp/images。版本对象的 inventory 关联目标路径为空（mapper 报 invalid association），只是告警。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">没有验证；重新构建后看 FirmwareVersion 和固件上传是否正常。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">curl -sk -u root:0penBmc https://127.0.0.1/redfish/v1/Managers/bmc | grep FirmwareVersion 应为 2.0.0。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J158" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bmcweb_%.bbappend</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="125" customHeight="1">
+      <x:c r="A159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 转储列表为空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">phosphor-debug-collector / bmcweb redfish-dump-log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">网页提示转储成功，但 Redfish Dump Entries 为空，dumps 目录也是空的；QEMU 里一次转储约 30 秒，期间再点会报 Another user initiated dump in progress。上次出现过的 entry/1 重启后不见了，原因没有查清。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需要点一次转储后抓 journalctl -u xyz.openbmc_project.Dump.Manager 的完整日志。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">转储完成后 busctl tree xyz.openbmc_project.Dump.Manager 应有 entry。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J159" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="125" customHeight="1">
+      <x:c r="A160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SD/eMMC 与硬件看门狗预超时</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts / ast2600-ceb-gnrd.dts（U-Boot）/ espi-peci.cfg</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本板没有 SD/eMMC，U-Boot 与 Linux 设备树都已禁用，去掉 mmc0: Failed to initialize a non-removable card。内核打开 CONFIG_WATCHDOG_PRETIMEOUT_GOV_PANIC，目的是去掉 systemd 的 pretimeout_governor 提示；aspeed_wdt 若不支持预超时，提示仍会存在，无害，看门狗 2 分钟复位不变。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Linux 设备树里的 emmc/emmc_controller/sdhci0/sdhci1/sdc 标签凭记忆写的，编译若报 undefined label 需改名。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">启动日志里不再有 mmc 行；ls /sys/class/watchdog/watchdog0/ 看是否有 pretimeout_governor。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J160" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts；espi-peci.cfg</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="125" customHeight="1">
+      <x:c r="A161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">板级自检脚本 ceb-gnrd-check</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">recipes-phosphor/utils/ceb-gnrd-check.bb</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">镜像自带 /usr/bin/ceb-gnrd-check，在 BMC 里运行，逐项输出 PASS/FAIL 并打包日志到 /tmp/ceb-gnrd-check.tar.gz。预期值按 QEMU 写，物理板上只有 info 项有意义。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上物理板后需要按实际硬件调整预期值（风扇、PECI、PSU、RTC 等）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">QEMU 里除 FirmwareVersion 外全部 PASS（共 50 项）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J161" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-check.bb；files/ceb-gnrd-check.sh；packagegroup-obmc-apps.bbappend</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="125" customHeight="1">
+      <x:c r="A162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">策略页与固件页精简</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0010、0012 网页补丁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">策略页移除 Virtual TPM 和 RTAD 两个开关（本板没有对应后端，只会报失败）；固件页 BIOS 区也去掉备份镜像卡片（BIOS 只有一个 flash bank）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">—</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">网页策略页只剩 SSH、IPMI、HTTP Basic、会话超时；固件页 BMC 和 BIOS 都只有执行镜像。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J162" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0010-ceb-gnrd-firmware-single-bank.patch；0012-ceb-gnrd-policies-remove-vtpm-rtad.patch</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7788,7 +7788,7 @@
       </x:c>
       <x:c r="B156" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">风扇设置写 Entity-Manager 报 InvalidArgs</x:t>
+          <x:t xml:space="preserve">风扇写 Entity-Manager 报 InvalidArgs（已解决）</x:t>
         </x:is>
       </x:c>
       <x:c r="C156" s="7" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </x:c>
       <x:c r="H156" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">原因待查（可能与 Entity-Manager 保存自己的 JSON 副本有关）；目前回读确认可以绕过。</x:t>
+          <x:t xml:space="preserve">已解决：服务写完回读确认，网页和 OEM 命令都已在 QEMU 里验证；Entity-Manager 返回错误的根因没有深究。</x:t>
         </x:is>
       </x:c>
       <x:c r="I156" s="7" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </x:c>
       <x:c r="B157" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">开机后一分钟内 ipmitool sensor 只有 2 个</x:t>
+          <x:t xml:space="preserve">开机后一分钟内 ipmitool sensor 只有 2 个（已解决）</x:t>
         </x:is>
       </x:c>
       <x:c r="C157" s="7" t="inlineStr">
@@ -7870,7 +7870,7 @@
       </x:c>
       <x:c r="H157" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上物理板后主机 BIOS 很早就用 KCS，要确认这个延迟是否可接受，必要时缩短上限。</x:t>
+          <x:t xml:space="preserve">已解决：ipmid 等传感器稳定后再启动，代价是开机后约一分钟 ipmitool 不可用；上物理板后确认这个延迟可接受。</x:t>
         </x:is>
       </x:c>
       <x:c r="I157" s="7" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </x:c>
       <x:c r="B159" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">BMC 转储列表为空</x:t>
+          <x:t xml:space="preserve">BMC 转储列表为空（已解决）</x:t>
         </x:is>
       </x:c>
       <x:c r="C159" s="7" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </x:c>
       <x:c r="H159" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需要点一次转储后抓 journalctl -u xyz.openbmc_project.Dump.Manager 的完整日志。</x:t>
+          <x:t xml:space="preserve">已解决：QEMU 里转储约 30 秒，点一次等完成即可，列表显示正常。</x:t>
         </x:is>
       </x:c>
       <x:c r="I159" s="7" t="inlineStr">

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -7996,7 +7996,7 @@
       </x:c>
       <x:c r="B160" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SD/eMMC 与硬件看门狗预超时</x:t>
+          <x:t xml:space="preserve">SD/eMMC 禁用与 BMC 硬件看门狗</x:t>
         </x:is>
       </x:c>
       <x:c r="C160" s="7" t="inlineStr">
@@ -8021,22 +8021,22 @@
       </x:c>
       <x:c r="G160" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本板没有 SD/eMMC，U-Boot 与 Linux 设备树都已禁用，去掉 mmc0: Failed to initialize a non-removable card。内核打开 CONFIG_WATCHDOG_PRETIMEOUT_GOV_PANIC，目的是去掉 systemd 的 pretimeout_governor 提示；aspeed_wdt 若不支持预超时，提示仍会存在，无害，看门狗 2 分钟复位不变。</x:t>
+          <x:t xml:space="preserve">本板没有 SD/eMMC，U-Boot 与 Linux 设备树都已禁用。WDT1 由 systemd 喂狗（120 秒），复位类型改为 soc（不是 system，避免 GPIO 回到上电状态让 CPLD/主机侧信号抖动）；aspeed_wdt 不支持预超时，已用 systemd 配置清掉 RuntimeWatchdogPreSec/PreGovernor，消除 pretimeout_governor 提示。内核 oops 转 panic、panic 5 秒后重启，打开 Magic SysRq 用于测试。新增 ceb-gnrd-health-monitor（服务卡死探测与重启、必要时强制重启 BMC）和 ceb-gnrd-wdt-reset-log（看门狗复位写 SEL）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H160" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Linux 设备树里的 emmc/emmc_controller/sdhci0/sdhci1/sdc 标签凭记忆写的，编译若报 undefined label 需改名。</x:t>
+          <x:t xml:space="preserve">上板要确认 soc 复位期间 CPLD 和主机侧信号（风扇接管、BIOS flash 选择、电源按键输出）电平稳定；启动早期（systemd 之前）是否有看门狗取决于 U-Boot；health monitor 和 wdt-reset-log 没有构建运行过；Linux 设备树里 emmc/sdhci 标签凭记忆写的。</x:t>
         </x:is>
       </x:c>
       <x:c r="I160" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">启动日志里不再有 mmc 行；ls /sys/class/watchdog/watchdog0/ 看是否有 pretimeout_governor。</x:t>
+          <x:t xml:space="preserve">echo c &gt; /proc/sysrq-trigger 应约 5 秒后自动重启，SEL 里有 BMC unexpected reset；echo 0 &gt; /proc/sys/kernel/panic 后再触发，约 2 分钟内被看门狗复位；kill -STOP 1 无效（内核忽略对 init 的 SIGSTOP）。</x:t>
         </x:is>
       </x:c>
       <x:c r="J160" s="7" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts；espi-peci.cfg</x:t>
+          <x:t xml:space="preserve">aspeed-ceb-gnrd.dts；ast2600-ceb-gnrd.dts；espi-peci.cfg；systemd-conf_%.bbappend；ceb-gnrd-health.bb</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/port_guide.xlsx
+++ b/port_guide.xlsx
@@ -8144,6 +8144,58 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="163" ht="125" customHeight="1">
+      <x:c r="A163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待澄清</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">与 OpenBMC 惯例对齐的改动</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conf/machine/ceb-gnrd.conf；ctopai-openbmc.conf；补丁文件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BMC 软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">软件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去掉 obmc-host-ctl（只有 OpenPOWER 的提供者）；obmc-discover-system-state 改为 x86-power-control（同 Intel 参考平台）；私有 D-Bus 名改为 com.ctopai.CebGnrd.*（对象路径仍在 /xyz 下，因为 bmcweb 的 D-Bus REST 只服务 /xyz 和 /org）；U-Boot、内核 Makefile、ipmitool 产品名由 sed 改成补丁；x86-power-control 和 ipmid 补丁按真实源码重新生成并去掉 patch-fuzz 降级；SEL rollover 改用标准 logrotate（约保留最新 100 到 200 条）；版本号放进 ctopai-openbmc 发行版；硬件契约不再用自造的机器特性。固件更新流程（bmcweb 的 updateservice 选项、经典更新服务）没有改，因为 BIOS 更新建立在经典流程上。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全部没有编译、没有验证；去掉 obmc-host-ctl 后要确认开关机正常；local.conf 必须选 ctopai-openbmc；logrotate 轮转后 SEL 记录 ID 是否连续要实测；ipmitool 的厂商名仍靠 enterprise-numbers 数据文件。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ceb-gnrd-check 回归；ipmitool mc info 的固件版本 2.00、厂商 CTOPAI、产品 CEB-GNR-D；制造 200 条以上 SEL 后 ipmitool sel list 只剩约 100 到 200 条；开关机和 chassis power 命令正常。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J163" s="7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conf/machine/ceb-gnrd.conf；meta-ctopai/conf/distro/ctopai-openbmc.conf；recipes-bsp/u-boot；recipes-kernel/linux；recipes-phosphor/ipmi；recipes-phosphor/sel-logger</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
